--- a/data/monthly/【2026年6月】月次数値.xlsx
+++ b/data/monthly/【2026年6月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="612" yWindow="528" windowWidth="21792" windowHeight="8868"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="236">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -590,31 +589,168 @@
   </si>
   <si>
     <t>2027-06-30</t>
+  </si>
+  <si>
+    <t>鍼灸サロンNOA</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2027-05-01</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック（2年目）</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科（2回目）</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>掛川整体院サウレ</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>アキュラデンタルクリニック</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>Healing Salon Ange</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -622,36 +758,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -940,14 +1076,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:Y119"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Y150"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1024,7 +1157,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -1053,7 +1186,7 @@
         <v>1.417411</v>
       </c>
       <c r="J2">
-        <v>47.4829932</v>
+        <v>47.482993200000003</v>
       </c>
       <c r="K2">
         <v>320</v>
@@ -1071,7 +1204,7 @@
         <v>4445</v>
       </c>
       <c r="P2">
-        <v>1570.303712</v>
+        <v>1570.3037119999999</v>
       </c>
       <c r="Q2">
         <v>147</v>
@@ -1080,16 +1213,16 @@
         <v>47.482993</v>
       </c>
       <c r="T2">
-        <v>3.307087</v>
+        <v>3.3070870000000001</v>
       </c>
       <c r="U2">
         <v>159</v>
       </c>
       <c r="V2">
-        <v>3.577053</v>
+        <v>3.5770529999999998</v>
       </c>
       <c r="W2">
-        <v>43.899371</v>
+        <v>43.899371000000002</v>
       </c>
       <c r="X2">
         <v>66</v>
@@ -1098,7 +1231,7 @@
         <v>105.757576</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1124,10 +1257,10 @@
         <v>2863</v>
       </c>
       <c r="I3">
-        <v>1.391198</v>
+        <v>1.3911979999999999</v>
       </c>
       <c r="J3">
-        <v>32.87755102</v>
+        <v>32.877551019999999</v>
       </c>
       <c r="K3">
         <v>160</v>
@@ -1151,10 +1284,10 @@
         <v>147</v>
       </c>
       <c r="S3">
-        <v>32.877551</v>
+        <v>32.877550999999997</v>
       </c>
       <c r="T3">
-        <v>3.690685</v>
+        <v>3.6906850000000002</v>
       </c>
       <c r="U3">
         <v>150</v>
@@ -1169,10 +1302,10 @@
         <v>107</v>
       </c>
       <c r="Y3">
-        <v>45.168224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>45.168224000000002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1198,7 +1331,7 @@
         <v>3732</v>
       </c>
       <c r="I4">
-        <v>1.255359</v>
+        <v>1.2553589999999999</v>
       </c>
       <c r="J4">
         <v>54.69318182</v>
@@ -1228,7 +1361,7 @@
         <v>54.693182</v>
       </c>
       <c r="T4">
-        <v>1.878335</v>
+        <v>1.8783350000000001</v>
       </c>
       <c r="U4">
         <v>91</v>
@@ -1243,10 +1376,10 @@
         <v>55</v>
       </c>
       <c r="Y4">
-        <v>87.509091</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>87.509090999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1275,7 +1408,7 @@
         <v>1.40615</v>
       </c>
       <c r="J5">
-        <v>47.83168317</v>
+        <v>47.831683169999998</v>
       </c>
       <c r="K5">
         <v>160</v>
@@ -1293,34 +1426,34 @@
         <v>4390</v>
       </c>
       <c r="P5">
-        <v>1100.455581</v>
+        <v>1100.4555809999999</v>
       </c>
       <c r="Q5">
         <v>101</v>
       </c>
       <c r="S5">
-        <v>47.831683</v>
+        <v>47.831682999999998</v>
       </c>
       <c r="T5">
-        <v>2.300683</v>
+        <v>2.3006829999999998</v>
       </c>
       <c r="U5">
         <v>118</v>
       </c>
       <c r="V5">
-        <v>2.687927</v>
+        <v>2.6879270000000002</v>
       </c>
       <c r="W5">
-        <v>40.940678</v>
+        <v>40.940677999999998</v>
       </c>
       <c r="X5">
         <v>73</v>
       </c>
       <c r="Y5">
-        <v>66.178082</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>66.178082000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1346,10 +1479,10 @@
         <v>2896</v>
       </c>
       <c r="I6">
-        <v>1.684047</v>
+        <v>1.6840470000000001</v>
       </c>
       <c r="J6">
-        <v>55.84883721</v>
+        <v>55.848837209999999</v>
       </c>
       <c r="K6">
         <v>160</v>
@@ -1367,13 +1500,13 @@
         <v>4877</v>
       </c>
       <c r="P6">
-        <v>984.826738</v>
+        <v>984.82673799999998</v>
       </c>
       <c r="Q6">
         <v>86</v>
       </c>
       <c r="S6">
-        <v>55.848837</v>
+        <v>55.848837000000003</v>
       </c>
       <c r="T6">
         <v>1.763379</v>
@@ -1385,16 +1518,16 @@
         <v>1.927414</v>
       </c>
       <c r="W6">
-        <v>51.095745</v>
+        <v>51.095745000000001</v>
       </c>
       <c r="X6">
         <v>54</v>
       </c>
       <c r="Y6">
-        <v>88.944444</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+        <v>88.944444000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1441,7 +1574,7 @@
         <v>4571</v>
       </c>
       <c r="P7">
-        <v>1055.567709</v>
+        <v>1055.5677089999999</v>
       </c>
       <c r="Q7">
         <v>125</v>
@@ -1450,25 +1583,25 @@
         <v>38.6</v>
       </c>
       <c r="T7">
-        <v>2.734631</v>
+        <v>2.7346309999999998</v>
       </c>
       <c r="U7">
         <v>149</v>
       </c>
       <c r="V7">
-        <v>3.259681</v>
+        <v>3.2596810000000001</v>
       </c>
       <c r="W7">
-        <v>32.38255</v>
+        <v>32.382550000000002</v>
       </c>
       <c r="X7">
         <v>88</v>
       </c>
       <c r="Y7">
-        <v>54.829545</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>54.829545000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1497,7 +1630,7 @@
         <v>1.328646</v>
       </c>
       <c r="J8">
-        <v>47.56435644</v>
+        <v>47.564356439999997</v>
       </c>
       <c r="K8">
         <v>160</v>
@@ -1515,13 +1648,13 @@
         <v>5102</v>
       </c>
       <c r="P8">
-        <v>941.591533</v>
+        <v>941.59153300000003</v>
       </c>
       <c r="Q8">
         <v>101</v>
       </c>
       <c r="S8">
-        <v>47.564356</v>
+        <v>47.564355999999997</v>
       </c>
       <c r="T8">
         <v>1.979616</v>
@@ -1530,19 +1663,19 @@
         <v>120</v>
       </c>
       <c r="V8">
-        <v>2.352019</v>
+        <v>2.3520189999999999</v>
       </c>
       <c r="W8">
-        <v>40.033333</v>
+        <v>40.033332999999999</v>
       </c>
       <c r="X8">
         <v>67</v>
       </c>
       <c r="Y8">
-        <v>71.701493</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>71.701492999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1568,10 +1701,10 @@
         <v>4451</v>
       </c>
       <c r="I9">
-        <v>1.197034</v>
+        <v>1.1970339999999999</v>
       </c>
       <c r="J9">
-        <v>49.2755102</v>
+        <v>49.275510199999999</v>
       </c>
       <c r="K9" t="s">
         <v>42</v>
@@ -1589,34 +1722,34 @@
         <v>5328</v>
       </c>
       <c r="P9">
-        <v>906.343844</v>
+        <v>906.34384399999999</v>
       </c>
       <c r="Q9">
         <v>123</v>
       </c>
       <c r="S9">
-        <v>39.260163</v>
+        <v>39.260162999999999</v>
       </c>
       <c r="T9">
-        <v>2.308559</v>
+        <v>2.3085589999999998</v>
       </c>
       <c r="U9">
         <v>165</v>
       </c>
       <c r="V9">
-        <v>3.096847</v>
+        <v>3.0968469999999999</v>
       </c>
       <c r="W9">
-        <v>29.266667</v>
+        <v>29.266667000000002</v>
       </c>
       <c r="X9">
         <v>98</v>
       </c>
       <c r="Y9">
-        <v>49.27551</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>49.275509999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1645,7 +1778,7 @@
         <v>1.154809</v>
       </c>
       <c r="J10">
-        <v>80.30645161</v>
+        <v>80.306451609999996</v>
       </c>
       <c r="K10" t="s">
         <v>42</v>
@@ -1663,34 +1796,34 @@
         <v>3506</v>
       </c>
       <c r="P10">
-        <v>1420.136908</v>
+        <v>1420.1369079999999</v>
       </c>
       <c r="Q10">
         <v>74</v>
       </c>
       <c r="S10">
-        <v>67.283784</v>
+        <v>67.283783999999997</v>
       </c>
       <c r="T10">
-        <v>2.110667</v>
+        <v>2.1106669999999998</v>
       </c>
       <c r="U10">
         <v>89</v>
       </c>
       <c r="V10">
-        <v>2.538505</v>
+        <v>2.5385049999999998</v>
       </c>
       <c r="W10">
-        <v>55.94382</v>
+        <v>55.943820000000002</v>
       </c>
       <c r="X10">
         <v>62</v>
       </c>
       <c r="Y10">
-        <v>80.306452</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>80.306451999999993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1719,7 +1852,7 @@
         <v>1.163904</v>
       </c>
       <c r="J11">
-        <v>69.32467532</v>
+        <v>69.324675319999997</v>
       </c>
       <c r="K11" t="s">
         <v>42</v>
@@ -1737,34 +1870,34 @@
         <v>3160</v>
       </c>
       <c r="P11">
-        <v>1689.240506</v>
+        <v>1689.2405060000001</v>
       </c>
       <c r="Q11">
         <v>88</v>
       </c>
       <c r="S11">
-        <v>60.659091</v>
+        <v>60.659090999999997</v>
       </c>
       <c r="T11">
-        <v>2.78481</v>
+        <v>2.7848099999999998</v>
       </c>
       <c r="U11">
         <v>94</v>
       </c>
       <c r="V11">
-        <v>2.974684</v>
+        <v>2.9746839999999999</v>
       </c>
       <c r="W11">
-        <v>56.787234</v>
+        <v>56.787233999999998</v>
       </c>
       <c r="X11">
         <v>77</v>
       </c>
       <c r="Y11">
-        <v>69.324675</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>69.324674999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1814,7 +1947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1843,7 +1976,7 @@
         <v>1.116852</v>
       </c>
       <c r="J13">
-        <v>70.05633803</v>
+        <v>70.056338030000006</v>
       </c>
       <c r="K13" t="s">
         <v>42</v>
@@ -1861,34 +1994,34 @@
         <v>3221</v>
       </c>
       <c r="P13">
-        <v>1544.240919</v>
+        <v>1544.2409190000001</v>
       </c>
       <c r="Q13">
         <v>91</v>
       </c>
       <c r="S13">
-        <v>54.659341</v>
+        <v>54.659340999999998</v>
       </c>
       <c r="T13">
-        <v>2.82521</v>
+        <v>2.8252100000000002</v>
       </c>
       <c r="U13">
         <v>88</v>
       </c>
       <c r="V13">
-        <v>2.732071</v>
+        <v>2.7320709999999999</v>
       </c>
       <c r="W13">
-        <v>56.522727</v>
+        <v>56.522727000000003</v>
       </c>
       <c r="X13">
         <v>71</v>
       </c>
       <c r="Y13">
-        <v>70.056338</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>70.056337999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1914,10 +2047,10 @@
         <v>2867</v>
       </c>
       <c r="I14">
-        <v>1.117544</v>
+        <v>1.1175440000000001</v>
       </c>
       <c r="J14">
-        <v>93.7037037</v>
+        <v>93.703703700000005</v>
       </c>
       <c r="K14" t="s">
         <v>42</v>
@@ -1941,10 +2074,10 @@
         <v>62</v>
       </c>
       <c r="S14">
-        <v>81.612903</v>
+        <v>81.612903000000003</v>
       </c>
       <c r="T14">
-        <v>1.935081</v>
+        <v>1.9350810000000001</v>
       </c>
       <c r="U14">
         <v>68</v>
@@ -1953,16 +2086,16 @@
         <v>2.122347</v>
       </c>
       <c r="W14">
-        <v>74.411765</v>
+        <v>74.411765000000003</v>
       </c>
       <c r="X14">
         <v>54</v>
       </c>
       <c r="Y14">
-        <v>93.703704</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>93.703704000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1988,7 +2121,7 @@
         <v>3757</v>
       </c>
       <c r="I15">
-        <v>1.296247</v>
+        <v>1.2962469999999999</v>
       </c>
       <c r="J15">
         <v>63.65</v>
@@ -2009,25 +2142,25 @@
         <v>4870</v>
       </c>
       <c r="P15">
-        <v>1045.585216</v>
+        <v>1045.5852159999999</v>
       </c>
       <c r="Q15">
         <v>92</v>
       </c>
       <c r="S15">
-        <v>55.347826</v>
+        <v>55.347825999999998</v>
       </c>
       <c r="T15">
-        <v>1.889117</v>
+        <v>1.8891169999999999</v>
       </c>
       <c r="U15">
         <v>129</v>
       </c>
       <c r="V15">
-        <v>2.648871</v>
+        <v>2.6488710000000002</v>
       </c>
       <c r="W15">
-        <v>39.472868</v>
+        <v>39.472867999999998</v>
       </c>
       <c r="X15">
         <v>80</v>
@@ -2036,7 +2169,7 @@
         <v>63.65</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -2062,7 +2195,7 @@
         <v>3583</v>
       </c>
       <c r="I16">
-        <v>1.354731</v>
+        <v>1.3547309999999999</v>
       </c>
       <c r="J16">
         <v>50.68</v>
@@ -2083,25 +2216,25 @@
         <v>4854</v>
       </c>
       <c r="P16">
-        <v>1044.087351</v>
+        <v>1044.0873509999999</v>
       </c>
       <c r="Q16">
         <v>129</v>
       </c>
       <c r="S16">
-        <v>39.286822</v>
+        <v>39.286822000000001</v>
       </c>
       <c r="T16">
-        <v>2.657602</v>
+        <v>2.6576019999999998</v>
       </c>
       <c r="U16">
         <v>144</v>
       </c>
       <c r="V16">
-        <v>2.966625</v>
+        <v>2.9666250000000001</v>
       </c>
       <c r="W16">
-        <v>35.194444</v>
+        <v>35.194443999999997</v>
       </c>
       <c r="X16">
         <v>100</v>
@@ -2110,7 +2243,7 @@
         <v>50.68</v>
       </c>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2136,10 +2269,10 @@
         <v>3136</v>
       </c>
       <c r="I17">
-        <v>1.295599</v>
+        <v>1.2955989999999999</v>
       </c>
       <c r="J17">
-        <v>94.81818182</v>
+        <v>94.818181820000007</v>
       </c>
       <c r="K17" t="s">
         <v>42</v>
@@ -2157,16 +2290,16 @@
         <v>4063</v>
       </c>
       <c r="P17">
-        <v>1283.534334</v>
+        <v>1283.5343339999999</v>
       </c>
       <c r="Q17">
         <v>75</v>
       </c>
       <c r="S17">
-        <v>69.533333</v>
+        <v>69.533332999999999</v>
       </c>
       <c r="T17">
-        <v>1.845927</v>
+        <v>1.8459270000000001</v>
       </c>
       <c r="U17">
         <v>90</v>
@@ -2175,16 +2308,16 @@
         <v>2.215112</v>
       </c>
       <c r="W17">
-        <v>57.944444</v>
+        <v>57.944443999999997</v>
       </c>
       <c r="X17">
         <v>55</v>
       </c>
       <c r="Y17">
-        <v>94.818182</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>94.818181999999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2210,7 +2343,7 @@
         <v>2707</v>
       </c>
       <c r="I18">
-        <v>1.338013</v>
+        <v>1.3380129999999999</v>
       </c>
       <c r="J18">
         <v>106.23404255</v>
@@ -2231,25 +2364,25 @@
         <v>3622</v>
       </c>
       <c r="P18">
-        <v>1378.520155</v>
+        <v>1378.5201549999999</v>
       </c>
       <c r="Q18">
         <v>59</v>
       </c>
       <c r="S18">
-        <v>84.627119</v>
+        <v>84.627118999999993</v>
       </c>
       <c r="T18">
-        <v>1.628934</v>
+        <v>1.6289340000000001</v>
       </c>
       <c r="U18">
         <v>62</v>
       </c>
       <c r="V18">
-        <v>1.711761</v>
+        <v>1.7117610000000001</v>
       </c>
       <c r="W18">
-        <v>80.532258</v>
+        <v>80.532257999999999</v>
       </c>
       <c r="X18">
         <v>47</v>
@@ -2258,7 +2391,7 @@
         <v>106.234043</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2284,10 +2417,10 @@
         <v>2967</v>
       </c>
       <c r="I19">
-        <v>1.430738</v>
+        <v>1.4307380000000001</v>
       </c>
       <c r="J19">
-        <v>75.1</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="K19" t="s">
         <v>42</v>
@@ -2311,7 +2444,7 @@
         <v>89</v>
       </c>
       <c r="S19">
-        <v>59.067416</v>
+        <v>59.067416000000001</v>
       </c>
       <c r="T19">
         <v>2.096584</v>
@@ -2320,19 +2453,19 @@
         <v>98</v>
       </c>
       <c r="V19">
-        <v>2.308598</v>
+        <v>2.3085979999999999</v>
       </c>
       <c r="W19">
-        <v>53.642857</v>
+        <v>53.642856999999999</v>
       </c>
       <c r="X19">
         <v>70</v>
       </c>
       <c r="Y19">
-        <v>75.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+        <v>75.099999999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2361,7 +2494,7 @@
         <v>1.235614</v>
       </c>
       <c r="J20">
-        <v>66.52631579</v>
+        <v>66.526315789999998</v>
       </c>
       <c r="K20" t="s">
         <v>42</v>
@@ -2388,25 +2521,25 @@
         <v>55.56044</v>
       </c>
       <c r="T20">
-        <v>3.337</v>
+        <v>3.3370000000000002</v>
       </c>
       <c r="U20">
         <v>102</v>
       </c>
       <c r="V20">
-        <v>3.740374</v>
+        <v>3.7403740000000001</v>
       </c>
       <c r="W20">
-        <v>49.568627</v>
+        <v>49.568626999999999</v>
       </c>
       <c r="X20">
         <v>76</v>
       </c>
       <c r="Y20">
-        <v>66.526316</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>66.526315999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2432,10 +2565,10 @@
         <v>3173</v>
       </c>
       <c r="I21">
-        <v>1.332178</v>
+        <v>1.3321780000000001</v>
       </c>
       <c r="J21">
-        <v>66.35</v>
+        <v>66.349999999999994</v>
       </c>
       <c r="K21" t="s">
         <v>42</v>
@@ -2453,13 +2586,13 @@
         <v>4227</v>
       </c>
       <c r="P21">
-        <v>1255.736929</v>
+        <v>1255.7369289999999</v>
       </c>
       <c r="Q21">
         <v>93</v>
       </c>
       <c r="S21">
-        <v>57.075269</v>
+        <v>57.075268999999999</v>
       </c>
       <c r="T21">
         <v>2.200142</v>
@@ -2468,19 +2601,19 @@
         <v>98</v>
       </c>
       <c r="V21">
-        <v>2.318429</v>
+        <v>2.3184290000000001</v>
       </c>
       <c r="W21">
-        <v>54.163265</v>
+        <v>54.163265000000003</v>
       </c>
       <c r="X21">
         <v>80</v>
       </c>
       <c r="Y21">
-        <v>66.35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>66.349999999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2533,10 +2666,10 @@
         <v>75</v>
       </c>
       <c r="S22">
-        <v>71.026667</v>
+        <v>71.026667000000003</v>
       </c>
       <c r="T22">
-        <v>1.504212</v>
+        <v>1.5042120000000001</v>
       </c>
       <c r="U22">
         <v>99</v>
@@ -2545,7 +2678,7 @@
         <v>1.98556</v>
       </c>
       <c r="W22">
-        <v>53.808081</v>
+        <v>53.808081000000001</v>
       </c>
       <c r="X22">
         <v>64</v>
@@ -2554,7 +2687,7 @@
         <v>83.234375</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2583,7 +2716,7 @@
         <v>1.195854</v>
       </c>
       <c r="J23">
-        <v>79.51388889</v>
+        <v>79.513888890000004</v>
       </c>
       <c r="K23" t="s">
         <v>42</v>
@@ -2607,10 +2740,10 @@
         <v>93</v>
       </c>
       <c r="S23">
-        <v>61.55914</v>
+        <v>61.559139999999999</v>
       </c>
       <c r="T23">
-        <v>2.12135</v>
+        <v>2.1213500000000001</v>
       </c>
       <c r="U23">
         <v>116</v>
@@ -2625,10 +2758,10 @@
         <v>72</v>
       </c>
       <c r="Y23">
-        <v>79.513889</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+        <v>79.513889000000006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2657,7 +2790,7 @@
         <v>1.294519</v>
       </c>
       <c r="J24">
-        <v>36.72483221</v>
+        <v>36.724832210000002</v>
       </c>
       <c r="K24" t="s">
         <v>42</v>
@@ -2675,22 +2808,22 @@
         <v>5503</v>
       </c>
       <c r="P24">
-        <v>994.366709</v>
+        <v>994.36670900000001</v>
       </c>
       <c r="Q24">
         <v>207</v>
       </c>
       <c r="S24">
-        <v>26.434783</v>
+        <v>26.434782999999999</v>
       </c>
       <c r="T24">
-        <v>3.761585</v>
+        <v>3.7615850000000002</v>
       </c>
       <c r="U24">
         <v>216</v>
       </c>
       <c r="V24">
-        <v>3.925132</v>
+        <v>3.9251320000000001</v>
       </c>
       <c r="W24">
         <v>25.333333</v>
@@ -2699,10 +2832,10 @@
         <v>149</v>
       </c>
       <c r="Y24">
-        <v>36.724832</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+        <v>36.724831999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2731,7 +2864,7 @@
         <v>1.126765</v>
       </c>
       <c r="J25">
-        <v>63.11827957</v>
+        <v>63.118279569999999</v>
       </c>
       <c r="K25" t="s">
         <v>42</v>
@@ -2749,34 +2882,34 @@
         <v>3751</v>
       </c>
       <c r="P25">
-        <v>1564.916022</v>
+        <v>1564.9160220000001</v>
       </c>
       <c r="Q25">
         <v>103</v>
       </c>
       <c r="S25">
-        <v>56.990291</v>
+        <v>56.990290999999999</v>
       </c>
       <c r="T25">
-        <v>2.745934</v>
+        <v>2.7459340000000001</v>
       </c>
       <c r="U25">
         <v>117</v>
       </c>
       <c r="V25">
-        <v>3.119168</v>
+        <v>3.1191680000000002</v>
       </c>
       <c r="W25">
-        <v>50.17094</v>
+        <v>50.170940000000002</v>
       </c>
       <c r="X25">
         <v>93</v>
       </c>
       <c r="Y25">
-        <v>63.11828</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
+        <v>63.118279999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2802,10 +2935,10 @@
         <v>6100</v>
       </c>
       <c r="I26">
-        <v>1.178689</v>
+        <v>1.1786890000000001</v>
       </c>
       <c r="J26">
-        <v>20.68235294</v>
+        <v>20.682352940000001</v>
       </c>
       <c r="K26" t="s">
         <v>42</v>
@@ -2829,10 +2962,10 @@
         <v>304</v>
       </c>
       <c r="S26">
-        <v>17.348684</v>
+        <v>17.348683999999999</v>
       </c>
       <c r="T26">
-        <v>4.228095</v>
+        <v>4.2280949999999997</v>
       </c>
       <c r="U26">
         <v>439</v>
@@ -2847,10 +2980,10 @@
         <v>255</v>
       </c>
       <c r="Y26">
-        <v>20.682353</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25">
+        <v>20.682352999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2876,10 +3009,10 @@
         <v>2670</v>
       </c>
       <c r="I27">
-        <v>1.395131</v>
+        <v>1.3951309999999999</v>
       </c>
       <c r="J27">
-        <v>79.32432432</v>
+        <v>79.324324320000002</v>
       </c>
       <c r="K27" t="s">
         <v>42</v>
@@ -2897,34 +3030,34 @@
         <v>3725</v>
       </c>
       <c r="P27">
-        <v>1575.838926</v>
+        <v>1575.8389259999999</v>
       </c>
       <c r="Q27">
         <v>83</v>
       </c>
       <c r="S27">
-        <v>70.722892</v>
+        <v>70.722892000000002</v>
       </c>
       <c r="T27">
-        <v>2.228188</v>
+        <v>2.2281879999999998</v>
       </c>
       <c r="U27">
         <v>91</v>
       </c>
       <c r="V27">
-        <v>2.442953</v>
+        <v>2.4429530000000002</v>
       </c>
       <c r="W27">
-        <v>64.505495</v>
+        <v>64.505494999999996</v>
       </c>
       <c r="X27">
         <v>74</v>
       </c>
       <c r="Y27">
-        <v>79.324324</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25">
+        <v>79.324324000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2950,10 +3083,10 @@
         <v>3122</v>
       </c>
       <c r="I28">
-        <v>1.128443</v>
+        <v>1.1284430000000001</v>
       </c>
       <c r="J28">
-        <v>71.51111111</v>
+        <v>71.511111110000002</v>
       </c>
       <c r="K28" t="s">
         <v>42</v>
@@ -2971,13 +3104,13 @@
         <v>3523</v>
       </c>
       <c r="P28">
-        <v>1826.852115</v>
+        <v>1826.8521149999999</v>
       </c>
       <c r="Q28">
         <v>98</v>
       </c>
       <c r="S28">
-        <v>65.673469</v>
+        <v>65.673468999999997</v>
       </c>
       <c r="T28">
         <v>2.78172</v>
@@ -2986,10 +3119,10 @@
         <v>104</v>
       </c>
       <c r="V28">
-        <v>2.95203</v>
+        <v>2.9520300000000002</v>
       </c>
       <c r="W28">
-        <v>61.884615</v>
+        <v>61.884614999999997</v>
       </c>
       <c r="X28">
         <v>90</v>
@@ -2998,7 +3131,7 @@
         <v>71.511111</v>
       </c>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -3027,7 +3160,7 @@
         <v>1.366962</v>
       </c>
       <c r="J29">
-        <v>66.39325843</v>
+        <v>66.393258430000003</v>
       </c>
       <c r="K29" t="s">
         <v>42</v>
@@ -3045,34 +3178,34 @@
         <v>4783</v>
       </c>
       <c r="P29">
-        <v>1235.417102</v>
+        <v>1235.4171020000001</v>
       </c>
       <c r="Q29">
         <v>101</v>
       </c>
       <c r="S29">
-        <v>58.504951</v>
+        <v>58.504950999999998</v>
       </c>
       <c r="T29">
-        <v>2.111645</v>
+        <v>2.1116450000000002</v>
       </c>
       <c r="U29">
         <v>127</v>
       </c>
       <c r="V29">
-        <v>2.655237</v>
+        <v>2.6552370000000001</v>
       </c>
       <c r="W29">
-        <v>46.527559</v>
+        <v>46.527558999999997</v>
       </c>
       <c r="X29">
         <v>89</v>
       </c>
       <c r="Y29">
-        <v>66.393258</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25">
+        <v>66.393258000000003</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -3098,10 +3231,10 @@
         <v>3996</v>
       </c>
       <c r="I30">
-        <v>1.254755</v>
+        <v>1.2547550000000001</v>
       </c>
       <c r="J30">
-        <v>98.03448276</v>
+        <v>98.034482760000003</v>
       </c>
       <c r="K30" t="s">
         <v>42</v>
@@ -3125,7 +3258,7 @@
         <v>87</v>
       </c>
       <c r="S30">
-        <v>65.356322</v>
+        <v>65.356322000000006</v>
       </c>
       <c r="T30">
         <v>1.735142</v>
@@ -3134,19 +3267,19 @@
         <v>110</v>
       </c>
       <c r="V30">
-        <v>2.193857</v>
+        <v>2.1938569999999999</v>
       </c>
       <c r="W30">
-        <v>51.690909</v>
+        <v>51.690908999999998</v>
       </c>
       <c r="X30">
         <v>58</v>
       </c>
       <c r="Y30">
-        <v>98.034483</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25">
+        <v>98.034482999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -3175,7 +3308,7 @@
         <v>1.082589</v>
       </c>
       <c r="J31">
-        <v>78.05405405</v>
+        <v>78.054054050000005</v>
       </c>
       <c r="K31" t="s">
         <v>42</v>
@@ -3199,7 +3332,7 @@
         <v>86</v>
       </c>
       <c r="S31">
-        <v>67.162791</v>
+        <v>67.162790999999999</v>
       </c>
       <c r="T31">
         <v>1.970218</v>
@@ -3208,7 +3341,7 @@
         <v>95</v>
       </c>
       <c r="V31">
-        <v>2.176403</v>
+        <v>2.1764030000000001</v>
       </c>
       <c r="W31">
         <v>60.8</v>
@@ -3217,10 +3350,10 @@
         <v>74</v>
       </c>
       <c r="Y31">
-        <v>78.054054</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25">
+        <v>78.054053999999994</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -3249,7 +3382,7 @@
         <v>1.360352</v>
       </c>
       <c r="J32">
-        <v>97.7704918</v>
+        <v>97.770491800000002</v>
       </c>
       <c r="K32" t="s">
         <v>42</v>
@@ -3273,7 +3406,7 @@
         <v>72</v>
       </c>
       <c r="S32">
-        <v>82.833333</v>
+        <v>82.833332999999996</v>
       </c>
       <c r="T32">
         <v>1.606784</v>
@@ -3285,16 +3418,16 @@
         <v>1.896898</v>
       </c>
       <c r="W32">
-        <v>70.164706</v>
+        <v>70.164705999999995</v>
       </c>
       <c r="X32">
         <v>61</v>
       </c>
       <c r="Y32">
-        <v>97.770492</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25">
+        <v>97.770492000000004</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -3320,7 +3453,7 @@
         <v>3802</v>
       </c>
       <c r="I33">
-        <v>1.146502</v>
+        <v>1.1465019999999999</v>
       </c>
       <c r="J33">
         <v>111.16363636</v>
@@ -3341,13 +3474,13 @@
         <v>4359</v>
       </c>
       <c r="P33">
-        <v>1402.615279</v>
+        <v>1402.6152790000001</v>
       </c>
       <c r="Q33">
         <v>67</v>
       </c>
       <c r="S33">
-        <v>91.253731</v>
+        <v>91.253731000000002</v>
       </c>
       <c r="T33">
         <v>1.53705</v>
@@ -3359,7 +3492,7 @@
         <v>1.927047</v>
       </c>
       <c r="W33">
-        <v>72.785714</v>
+        <v>72.785713999999999</v>
       </c>
       <c r="X33">
         <v>55</v>
@@ -3368,7 +3501,7 @@
         <v>111.163636</v>
       </c>
     </row>
-    <row r="34" spans="1:25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -3397,7 +3530,7 @@
         <v>1.356789</v>
       </c>
       <c r="J34">
-        <v>39.21527778</v>
+        <v>39.215277780000001</v>
       </c>
       <c r="K34" t="s">
         <v>42</v>
@@ -3424,25 +3557,25 @@
         <v>31.198895</v>
       </c>
       <c r="T34">
-        <v>3.150017</v>
+        <v>3.1500170000000001</v>
       </c>
       <c r="U34">
         <v>204</v>
       </c>
       <c r="V34">
-        <v>3.550296</v>
+        <v>3.5502959999999999</v>
       </c>
       <c r="W34">
-        <v>27.681373</v>
+        <v>27.681373000000001</v>
       </c>
       <c r="X34">
         <v>144</v>
       </c>
       <c r="Y34">
-        <v>39.215278</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
+        <v>39.215277999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -3468,7 +3601,7 @@
         <v>2888</v>
       </c>
       <c r="I35">
-        <v>1.385042</v>
+        <v>1.3850420000000001</v>
       </c>
       <c r="J35">
         <v>96.32</v>
@@ -3504,7 +3637,7 @@
         <v>83</v>
       </c>
       <c r="V35">
-        <v>2.075</v>
+        <v>2.0750000000000002</v>
       </c>
       <c r="W35">
         <v>58.024096</v>
@@ -3516,7 +3649,7 @@
         <v>96.32</v>
       </c>
     </row>
-    <row r="36" spans="1:25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -3545,7 +3678,7 @@
         <v>1.213211</v>
       </c>
       <c r="J36">
-        <v>59.51851852</v>
+        <v>59.518518520000001</v>
       </c>
       <c r="K36" t="s">
         <v>42</v>
@@ -3569,10 +3702,10 @@
         <v>88</v>
       </c>
       <c r="S36">
-        <v>54.784091</v>
+        <v>54.784090999999997</v>
       </c>
       <c r="T36">
-        <v>2.139037</v>
+        <v>2.1390370000000001</v>
       </c>
       <c r="U36">
         <v>102</v>
@@ -3581,16 +3714,16 @@
         <v>2.479339</v>
       </c>
       <c r="W36">
-        <v>47.264706</v>
+        <v>47.264705999999997</v>
       </c>
       <c r="X36">
         <v>81</v>
       </c>
       <c r="Y36">
-        <v>59.518519</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25">
+        <v>59.518518999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -3616,7 +3749,7 @@
         <v>3076</v>
       </c>
       <c r="I37">
-        <v>1.203186</v>
+        <v>1.2031860000000001</v>
       </c>
       <c r="J37">
         <v>57.26190476</v>
@@ -3637,7 +3770,7 @@
         <v>3701</v>
       </c>
       <c r="P37">
-        <v>1299.648744</v>
+        <v>1299.6487440000001</v>
       </c>
       <c r="Q37">
         <v>93</v>
@@ -3646,25 +3779,25 @@
         <v>51.72043</v>
       </c>
       <c r="T37">
-        <v>2.512834</v>
+        <v>2.5128339999999998</v>
       </c>
       <c r="U37">
         <v>124</v>
       </c>
       <c r="V37">
-        <v>3.350446</v>
+        <v>3.3504459999999998</v>
       </c>
       <c r="W37">
-        <v>38.790323</v>
+        <v>38.790323000000001</v>
       </c>
       <c r="X37">
         <v>84</v>
       </c>
       <c r="Y37">
-        <v>57.261905</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25">
+        <v>57.261904999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -3690,10 +3823,10 @@
         <v>3873</v>
       </c>
       <c r="I38">
-        <v>1.38394</v>
+        <v>1.3839399999999999</v>
       </c>
       <c r="J38">
-        <v>61.66666667</v>
+        <v>61.666666669999998</v>
       </c>
       <c r="K38" t="s">
         <v>42</v>
@@ -3717,28 +3850,28 @@
         <v>89</v>
       </c>
       <c r="S38">
-        <v>54.044944</v>
+        <v>54.044944000000001</v>
       </c>
       <c r="T38">
-        <v>1.660448</v>
+        <v>1.6604479999999999</v>
       </c>
       <c r="U38">
         <v>137</v>
       </c>
       <c r="V38">
-        <v>2.55597</v>
+        <v>2.5559699999999999</v>
       </c>
       <c r="W38">
-        <v>35.109489</v>
+        <v>35.109489000000004</v>
       </c>
       <c r="X38">
         <v>78</v>
       </c>
       <c r="Y38">
-        <v>61.666667</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
+        <v>61.666666999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -3764,10 +3897,10 @@
         <v>2719</v>
       </c>
       <c r="I39">
-        <v>1.348658</v>
+        <v>1.3486579999999999</v>
       </c>
       <c r="J39">
-        <v>55.45348837</v>
+        <v>55.453488370000002</v>
       </c>
       <c r="K39" t="s">
         <v>42</v>
@@ -3794,16 +3927,16 @@
         <v>47.69</v>
       </c>
       <c r="T39">
-        <v>2.727025</v>
+        <v>2.7270249999999998</v>
       </c>
       <c r="U39">
         <v>119</v>
       </c>
       <c r="V39">
-        <v>3.24516</v>
+        <v>3.2451599999999998</v>
       </c>
       <c r="W39">
-        <v>40.07563</v>
+        <v>40.075629999999997</v>
       </c>
       <c r="X39">
         <v>86</v>
@@ -3812,7 +3945,7 @@
         <v>55.453488</v>
       </c>
     </row>
-    <row r="40" spans="1:25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -3841,7 +3974,7 @@
         <v>1.249876</v>
       </c>
       <c r="J40">
-        <v>26.64088398</v>
+        <v>26.640883980000002</v>
       </c>
       <c r="K40" t="s">
         <v>42</v>
@@ -3859,25 +3992,25 @@
         <v>5057</v>
       </c>
       <c r="P40">
-        <v>953.529761</v>
+        <v>953.52976100000001</v>
       </c>
       <c r="Q40">
         <v>212</v>
       </c>
       <c r="S40">
-        <v>22.745283</v>
+        <v>22.745283000000001</v>
       </c>
       <c r="T40">
-        <v>4.192209</v>
+        <v>4.1922090000000001</v>
       </c>
       <c r="U40">
         <v>240</v>
       </c>
       <c r="V40">
-        <v>4.745897</v>
+        <v>4.7458970000000003</v>
       </c>
       <c r="W40">
-        <v>20.091667</v>
+        <v>20.091667000000001</v>
       </c>
       <c r="X40">
         <v>181</v>
@@ -3886,7 +4019,7 @@
         <v>26.640884</v>
       </c>
     </row>
-    <row r="41" spans="1:25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -3915,7 +4048,7 @@
         <v>1.279207</v>
       </c>
       <c r="J41">
-        <v>49.15463918</v>
+        <v>49.154639179999997</v>
       </c>
       <c r="K41" t="s">
         <v>42</v>
@@ -3933,34 +4066,34 @@
         <v>4774</v>
       </c>
       <c r="P41">
-        <v>998.743192</v>
+        <v>998.74319200000002</v>
       </c>
       <c r="Q41">
         <v>118</v>
       </c>
       <c r="S41">
-        <v>40.40678</v>
+        <v>40.406779999999998</v>
       </c>
       <c r="T41">
-        <v>2.471722</v>
+        <v>2.4717220000000002</v>
       </c>
       <c r="U41">
         <v>140</v>
       </c>
       <c r="V41">
-        <v>2.932551</v>
+        <v>2.9325510000000001</v>
       </c>
       <c r="W41">
-        <v>34.057143</v>
+        <v>34.057143000000003</v>
       </c>
       <c r="X41">
         <v>97</v>
       </c>
       <c r="Y41">
-        <v>49.154639</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25">
+        <v>49.154639000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -3986,7 +4119,7 @@
         <v>3636</v>
       </c>
       <c r="I42">
-        <v>1.137514</v>
+        <v>1.1375139999999999</v>
       </c>
       <c r="J42">
         <v>67.875</v>
@@ -4007,25 +4140,25 @@
         <v>4136</v>
       </c>
       <c r="P42">
-        <v>1181.576402</v>
+        <v>1181.5764019999999</v>
       </c>
       <c r="Q42">
         <v>91</v>
       </c>
       <c r="S42">
-        <v>53.703297</v>
+        <v>53.703296999999999</v>
       </c>
       <c r="T42">
-        <v>2.200193</v>
+        <v>2.2001930000000001</v>
       </c>
       <c r="U42">
         <v>111</v>
       </c>
       <c r="V42">
-        <v>2.683752</v>
+        <v>2.6837520000000001</v>
       </c>
       <c r="W42">
-        <v>44.027027</v>
+        <v>44.027026999999997</v>
       </c>
       <c r="X42">
         <v>72</v>
@@ -4034,7 +4167,7 @@
         <v>67.875</v>
       </c>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -4063,7 +4196,7 @@
         <v>1.30627</v>
       </c>
       <c r="J43">
-        <v>43.97247706</v>
+        <v>43.972477060000003</v>
       </c>
       <c r="K43" t="s">
         <v>42</v>
@@ -4081,34 +4214,34 @@
         <v>4875</v>
       </c>
       <c r="P43">
-        <v>983.179487</v>
+        <v>983.17948699999999</v>
       </c>
       <c r="Q43">
         <v>129</v>
       </c>
       <c r="S43">
-        <v>37.155039</v>
+        <v>37.155039000000002</v>
       </c>
       <c r="T43">
-        <v>2.646154</v>
+        <v>2.6461540000000001</v>
       </c>
       <c r="U43">
         <v>136</v>
       </c>
       <c r="V43">
-        <v>2.789744</v>
+        <v>2.7897439999999998</v>
       </c>
       <c r="W43">
-        <v>35.242647</v>
+        <v>35.242646999999998</v>
       </c>
       <c r="X43">
         <v>109</v>
       </c>
       <c r="Y43">
-        <v>43.972477</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25">
+        <v>43.972476999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -4137,7 +4270,7 @@
         <v>1.349647</v>
       </c>
       <c r="J44">
-        <v>41.08547009</v>
+        <v>41.085470090000001</v>
       </c>
       <c r="K44" t="s">
         <v>42</v>
@@ -4155,34 +4288,34 @@
         <v>3254</v>
       </c>
       <c r="P44">
-        <v>1477.258758</v>
+        <v>1477.2587579999999</v>
       </c>
       <c r="Q44">
         <v>128</v>
       </c>
       <c r="S44">
-        <v>37.554688</v>
+        <v>37.554687999999999</v>
       </c>
       <c r="T44">
-        <v>3.93362</v>
+        <v>3.9336199999999999</v>
       </c>
       <c r="U44">
         <v>143</v>
       </c>
       <c r="V44">
-        <v>4.394591</v>
+        <v>4.3945910000000001</v>
       </c>
       <c r="W44">
-        <v>33.615385</v>
+        <v>33.615385000000003</v>
       </c>
       <c r="X44">
         <v>117</v>
       </c>
       <c r="Y44">
-        <v>41.08547</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25">
+        <v>41.085470000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -4211,7 +4344,7 @@
         <v>1.175325</v>
       </c>
       <c r="J45">
-        <v>73.33846154</v>
+        <v>73.338461539999997</v>
       </c>
       <c r="K45" t="s">
         <v>42</v>
@@ -4229,34 +4362,34 @@
         <v>2896</v>
       </c>
       <c r="P45">
-        <v>1646.063536</v>
+        <v>1646.0635360000001</v>
       </c>
       <c r="Q45">
         <v>74</v>
       </c>
       <c r="S45">
-        <v>64.418919</v>
+        <v>64.418919000000002</v>
       </c>
       <c r="T45">
-        <v>2.555249</v>
+        <v>2.5552489999999999</v>
       </c>
       <c r="U45">
         <v>80</v>
       </c>
       <c r="V45">
-        <v>2.762431</v>
+        <v>2.7624309999999999</v>
       </c>
       <c r="W45">
-        <v>59.5875</v>
+        <v>59.587499999999999</v>
       </c>
       <c r="X45">
         <v>65</v>
       </c>
       <c r="Y45">
-        <v>73.338462</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25">
+        <v>73.338462000000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>25</v>
       </c>
@@ -4285,7 +4418,7 @@
         <v>1.316357</v>
       </c>
       <c r="J46">
-        <v>27.30113636</v>
+        <v>27.301136360000001</v>
       </c>
       <c r="K46" t="s">
         <v>42</v>
@@ -4303,7 +4436,7 @@
         <v>4032</v>
       </c>
       <c r="P46">
-        <v>1191.71627</v>
+        <v>1191.7162699999999</v>
       </c>
       <c r="Q46">
         <v>192</v>
@@ -4312,13 +4445,13 @@
         <v>25.026042</v>
       </c>
       <c r="T46">
-        <v>4.761905</v>
+        <v>4.7619049999999996</v>
       </c>
       <c r="U46">
         <v>254</v>
       </c>
       <c r="V46">
-        <v>6.299603</v>
+        <v>6.2996030000000003</v>
       </c>
       <c r="W46">
         <v>18.917323</v>
@@ -4330,7 +4463,7 @@
         <v>27.301136</v>
       </c>
     </row>
-    <row r="47" spans="1:25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -4377,34 +4510,34 @@
         <v>5410</v>
       </c>
       <c r="P47">
-        <v>893.530499</v>
+        <v>893.53049899999996</v>
       </c>
       <c r="Q47">
         <v>72</v>
       </c>
       <c r="S47">
-        <v>67.138889</v>
+        <v>67.138889000000006</v>
       </c>
       <c r="T47">
-        <v>1.330869</v>
+        <v>1.3308690000000001</v>
       </c>
       <c r="U47">
         <v>89</v>
       </c>
       <c r="V47">
-        <v>1.645102</v>
+        <v>1.6451020000000001</v>
       </c>
       <c r="W47">
-        <v>54.314607</v>
+        <v>54.314607000000002</v>
       </c>
       <c r="X47">
         <v>61</v>
       </c>
       <c r="Y47">
-        <v>79.245902</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25">
+        <v>79.245902000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -4451,13 +4584,13 @@
         <v>9546</v>
       </c>
       <c r="P48">
-        <v>996.857322</v>
+        <v>996.85732199999995</v>
       </c>
       <c r="Q48">
         <v>109</v>
       </c>
       <c r="S48">
-        <v>87.302752</v>
+        <v>87.302751999999998</v>
       </c>
       <c r="T48">
         <v>1.14184</v>
@@ -4469,16 +4602,16 @@
         <v>1.319925</v>
       </c>
       <c r="W48">
-        <v>75.52381</v>
+        <v>75.523809999999997</v>
       </c>
       <c r="X48">
         <v>71</v>
       </c>
       <c r="Y48">
-        <v>134.028169</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25">
+        <v>134.02816899999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -4528,7 +4661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -4554,10 +4687,10 @@
         <v>6479</v>
       </c>
       <c r="I50">
-        <v>1.289705</v>
+        <v>1.2897050000000001</v>
       </c>
       <c r="J50">
-        <v>77.02419355</v>
+        <v>77.024193550000007</v>
       </c>
       <c r="K50" t="s">
         <v>42</v>
@@ -4575,7 +4708,7 @@
         <v>8356</v>
       </c>
       <c r="P50">
-        <v>1143.01101</v>
+        <v>1143.0110099999999</v>
       </c>
       <c r="Q50">
         <v>174</v>
@@ -4584,25 +4717,25 @@
         <v>54.890805</v>
       </c>
       <c r="T50">
-        <v>2.082336</v>
+        <v>2.0823360000000002</v>
       </c>
       <c r="U50">
         <v>190</v>
       </c>
       <c r="V50">
-        <v>2.273815</v>
+        <v>2.2738149999999999</v>
       </c>
       <c r="W50">
-        <v>50.268421</v>
+        <v>50.268420999999996</v>
       </c>
       <c r="X50">
         <v>124</v>
       </c>
       <c r="Y50">
-        <v>77.024194</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25">
+        <v>77.024193999999994</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -4631,7 +4764,7 @@
         <v>1.452617</v>
       </c>
       <c r="J51">
-        <v>54.80571429</v>
+        <v>54.805714289999997</v>
       </c>
       <c r="K51" t="s">
         <v>42</v>
@@ -4655,10 +4788,10 @@
         <v>201</v>
       </c>
       <c r="S51">
-        <v>47.716418</v>
+        <v>47.716417999999997</v>
       </c>
       <c r="T51">
-        <v>2.366934</v>
+        <v>2.3669340000000001</v>
       </c>
       <c r="U51">
         <v>247</v>
@@ -4673,10 +4806,10 @@
         <v>175</v>
       </c>
       <c r="Y51">
-        <v>54.805714</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25">
+        <v>54.805714000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -4726,7 +4859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -4773,34 +4906,34 @@
         <v>3712</v>
       </c>
       <c r="P53">
-        <v>1303.340517</v>
+        <v>1303.3405170000001</v>
       </c>
       <c r="Q53">
         <v>93</v>
       </c>
       <c r="S53">
-        <v>52.021505</v>
+        <v>52.021504999999998</v>
       </c>
       <c r="T53">
-        <v>2.505388</v>
+        <v>2.5053879999999999</v>
       </c>
       <c r="U53">
         <v>108</v>
       </c>
       <c r="V53">
-        <v>2.909483</v>
+        <v>2.9094829999999998</v>
       </c>
       <c r="W53">
-        <v>44.796296</v>
+        <v>44.796295999999998</v>
       </c>
       <c r="X53">
         <v>85</v>
       </c>
       <c r="Y53">
-        <v>56.917647</v>
-      </c>
-    </row>
-    <row r="54" spans="1:25">
+        <v>56.917647000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -4826,10 +4959,10 @@
         <v>6572</v>
       </c>
       <c r="I54">
-        <v>1.347079</v>
+        <v>1.3470789999999999</v>
       </c>
       <c r="J54">
-        <v>88.5412844</v>
+        <v>88.541284399999995</v>
       </c>
       <c r="K54" t="s">
         <v>42</v>
@@ -4847,13 +4980,13 @@
         <v>8853</v>
       </c>
       <c r="P54">
-        <v>1090.138936</v>
+        <v>1090.1389360000001</v>
       </c>
       <c r="Q54">
         <v>127</v>
       </c>
       <c r="S54">
-        <v>75.992126</v>
+        <v>75.992125999999999</v>
       </c>
       <c r="T54">
         <v>1.434542</v>
@@ -4862,19 +4995,19 @@
         <v>139</v>
       </c>
       <c r="V54">
-        <v>1.570089</v>
+        <v>1.5700890000000001</v>
       </c>
       <c r="W54">
-        <v>69.431655</v>
+        <v>69.431655000000006</v>
       </c>
       <c r="X54">
         <v>109</v>
       </c>
       <c r="Y54">
-        <v>88.541284</v>
-      </c>
-    </row>
-    <row r="55" spans="1:25">
+        <v>88.541284000000005</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -4900,10 +5033,10 @@
         <v>9332</v>
       </c>
       <c r="I55">
-        <v>1.168667</v>
+        <v>1.1686669999999999</v>
       </c>
       <c r="J55">
-        <v>72.8030303</v>
+        <v>72.803030300000003</v>
       </c>
       <c r="K55" t="s">
         <v>42</v>
@@ -4921,7 +5054,7 @@
         <v>10906</v>
       </c>
       <c r="P55">
-        <v>881.16633</v>
+        <v>881.16633000000002</v>
       </c>
       <c r="Q55">
         <v>155</v>
@@ -4930,25 +5063,25 @@
         <v>62</v>
       </c>
       <c r="T55">
-        <v>1.421236</v>
+        <v>1.4212359999999999</v>
       </c>
       <c r="U55">
         <v>167</v>
       </c>
       <c r="V55">
-        <v>1.531267</v>
+        <v>1.5312669999999999</v>
       </c>
       <c r="W55">
-        <v>57.54491</v>
+        <v>57.544910000000002</v>
       </c>
       <c r="X55">
         <v>132</v>
       </c>
       <c r="Y55">
-        <v>72.80303</v>
-      </c>
-    </row>
-    <row r="56" spans="1:25">
+        <v>72.803030000000007</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -4974,10 +5107,10 @@
         <v>7657</v>
       </c>
       <c r="I56">
-        <v>1.192112</v>
+        <v>1.1921120000000001</v>
       </c>
       <c r="J56">
-        <v>85.75221239</v>
+        <v>85.752212389999997</v>
       </c>
       <c r="K56" t="s">
         <v>42</v>
@@ -4995,25 +5128,25 @@
         <v>9128</v>
       </c>
       <c r="P56">
-        <v>1061.568799</v>
+        <v>1061.5687989999999</v>
       </c>
       <c r="Q56">
         <v>132</v>
       </c>
       <c r="S56">
-        <v>73.409091</v>
+        <v>73.409091000000004</v>
       </c>
       <c r="T56">
-        <v>1.4461</v>
+        <v>1.4460999999999999</v>
       </c>
       <c r="U56">
         <v>146</v>
       </c>
       <c r="V56">
-        <v>1.599474</v>
+        <v>1.5994740000000001</v>
       </c>
       <c r="W56">
-        <v>66.369863</v>
+        <v>66.369862999999995</v>
       </c>
       <c r="X56">
         <v>113</v>
@@ -5022,7 +5155,7 @@
         <v>85.752212</v>
       </c>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -5048,10 +5181,10 @@
         <v>2997</v>
       </c>
       <c r="I57">
-        <v>1.1001</v>
+        <v>1.1001000000000001</v>
       </c>
       <c r="J57">
-        <v>69.38636364</v>
+        <v>69.386363639999999</v>
       </c>
       <c r="K57" t="s">
         <v>42</v>
@@ -5069,13 +5202,13 @@
         <v>3297</v>
       </c>
       <c r="P57">
-        <v>925.993327</v>
+        <v>925.99332700000002</v>
       </c>
       <c r="Q57">
         <v>51</v>
       </c>
       <c r="S57">
-        <v>59.862745</v>
+        <v>59.862744999999997</v>
       </c>
       <c r="T57">
         <v>1.546861</v>
@@ -5084,10 +5217,10 @@
         <v>62</v>
       </c>
       <c r="V57">
-        <v>1.880497</v>
+        <v>1.8804970000000001</v>
       </c>
       <c r="W57">
-        <v>49.241935</v>
+        <v>49.241934999999998</v>
       </c>
       <c r="X57">
         <v>44</v>
@@ -5096,7 +5229,7 @@
         <v>69.386364</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -5146,7 +5279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>25</v>
       </c>
@@ -5172,7 +5305,7 @@
         <v>3145</v>
       </c>
       <c r="I59">
-        <v>1.624801</v>
+        <v>1.6248009999999999</v>
       </c>
       <c r="J59">
         <v>18.39463602</v>
@@ -5193,7 +5326,7 @@
         <v>5110</v>
       </c>
       <c r="P59">
-        <v>939.530333</v>
+        <v>939.53033300000004</v>
       </c>
       <c r="Q59">
         <v>299</v>
@@ -5202,13 +5335,13 @@
         <v>16.056856</v>
       </c>
       <c r="T59">
-        <v>5.851272</v>
+        <v>5.8512719999999998</v>
       </c>
       <c r="U59">
         <v>374</v>
       </c>
       <c r="V59">
-        <v>7.318982</v>
+        <v>7.3189820000000001</v>
       </c>
       <c r="W59">
         <v>12.836898</v>
@@ -5217,10 +5350,10 @@
         <v>261</v>
       </c>
       <c r="Y59">
-        <v>18.394636</v>
-      </c>
-    </row>
-    <row r="60" spans="1:25">
+        <v>18.394635999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -5246,10 +5379,10 @@
         <v>3477</v>
       </c>
       <c r="I60">
-        <v>1.351452</v>
+        <v>1.3514520000000001</v>
       </c>
       <c r="J60">
-        <v>59.94936709</v>
+        <v>59.949367090000003</v>
       </c>
       <c r="K60" t="s">
         <v>42</v>
@@ -5273,28 +5406,28 @@
         <v>90</v>
       </c>
       <c r="S60">
-        <v>52.622222</v>
+        <v>52.622222000000001</v>
       </c>
       <c r="T60">
-        <v>1.915301</v>
+        <v>1.9153009999999999</v>
       </c>
       <c r="U60">
         <v>104</v>
       </c>
       <c r="V60">
-        <v>2.213237</v>
+        <v>2.2132369999999999</v>
       </c>
       <c r="W60">
-        <v>45.538462</v>
+        <v>45.538462000000003</v>
       </c>
       <c r="X60">
         <v>79</v>
       </c>
       <c r="Y60">
-        <v>59.949367</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25">
+        <v>59.949367000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>25</v>
       </c>
@@ -5320,10 +5453,10 @@
         <v>3428</v>
       </c>
       <c r="I61">
-        <v>1.317678</v>
+        <v>1.3176779999999999</v>
       </c>
       <c r="J61">
-        <v>29.81481481</v>
+        <v>29.814814810000001</v>
       </c>
       <c r="K61" t="s">
         <v>42</v>
@@ -5341,22 +5474,22 @@
         <v>4517</v>
       </c>
       <c r="P61">
-        <v>1069.293779</v>
+        <v>1069.2937790000001</v>
       </c>
       <c r="Q61">
         <v>183</v>
       </c>
       <c r="S61">
-        <v>26.393443</v>
+        <v>26.393443000000001</v>
       </c>
       <c r="T61">
-        <v>4.051362</v>
+        <v>4.0513620000000001</v>
       </c>
       <c r="U61">
         <v>222</v>
       </c>
       <c r="V61">
-        <v>4.914766</v>
+        <v>4.9147660000000002</v>
       </c>
       <c r="W61">
         <v>21.756757</v>
@@ -5365,10 +5498,10 @@
         <v>162</v>
       </c>
       <c r="Y61">
-        <v>29.814815</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25">
+        <v>29.814814999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>25</v>
       </c>
@@ -5394,7 +5527,7 @@
         <v>3206</v>
       </c>
       <c r="I62">
-        <v>1.278852</v>
+        <v>1.2788520000000001</v>
       </c>
       <c r="J62">
         <v>52.67777778</v>
@@ -5421,7 +5554,7 @@
         <v>98</v>
       </c>
       <c r="S62">
-        <v>48.377551</v>
+        <v>48.377550999999997</v>
       </c>
       <c r="T62">
         <v>2.390244</v>
@@ -5430,19 +5563,19 @@
         <v>119</v>
       </c>
       <c r="V62">
-        <v>2.902439</v>
+        <v>2.9024390000000002</v>
       </c>
       <c r="W62">
-        <v>39.840336</v>
+        <v>39.840336000000001</v>
       </c>
       <c r="X62">
         <v>90</v>
       </c>
       <c r="Y62">
-        <v>52.677778</v>
-      </c>
-    </row>
-    <row r="63" spans="1:25">
+        <v>52.677778000000004</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -5471,7 +5604,7 @@
         <v>1.161165</v>
       </c>
       <c r="J63">
-        <v>65.7260274</v>
+        <v>65.726027400000007</v>
       </c>
       <c r="K63" t="s">
         <v>42</v>
@@ -5489,7 +5622,7 @@
         <v>3588</v>
       </c>
       <c r="P63">
-        <v>1337.235229</v>
+        <v>1337.2352289999999</v>
       </c>
       <c r="Q63">
         <v>83</v>
@@ -5504,19 +5637,19 @@
         <v>94</v>
       </c>
       <c r="V63">
-        <v>2.619844</v>
+        <v>2.6198440000000001</v>
       </c>
       <c r="W63">
-        <v>51.042553</v>
+        <v>51.042552999999998</v>
       </c>
       <c r="X63">
         <v>73</v>
       </c>
       <c r="Y63">
-        <v>65.726027</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25">
+        <v>65.726027000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -5569,28 +5702,28 @@
         <v>92</v>
       </c>
       <c r="S64">
-        <v>52.119565</v>
+        <v>52.119565000000001</v>
       </c>
       <c r="T64">
-        <v>3.629191</v>
+        <v>3.6291910000000001</v>
       </c>
       <c r="U64">
         <v>96</v>
       </c>
       <c r="V64">
-        <v>3.786982</v>
+        <v>3.7869820000000001</v>
       </c>
       <c r="W64">
-        <v>49.947917</v>
+        <v>49.947916999999997</v>
       </c>
       <c r="X64">
         <v>85</v>
       </c>
       <c r="Y64">
-        <v>56.411765</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25">
+        <v>56.411765000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -5619,7 +5752,7 @@
         <v>1.428304</v>
       </c>
       <c r="J65">
-        <v>54.07865169</v>
+        <v>54.078651690000001</v>
       </c>
       <c r="K65" t="s">
         <v>42</v>
@@ -5643,7 +5776,7 @@
         <v>108</v>
       </c>
       <c r="S65">
-        <v>44.564815</v>
+        <v>44.564815000000003</v>
       </c>
       <c r="T65">
         <v>2.019069</v>
@@ -5655,16 +5788,16 @@
         <v>2.598617</v>
       </c>
       <c r="W65">
-        <v>34.625899</v>
+        <v>34.625898999999997</v>
       </c>
       <c r="X65">
         <v>89</v>
       </c>
       <c r="Y65">
-        <v>54.078652</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25">
+        <v>54.078651999999998</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -5693,7 +5826,7 @@
         <v>1.254067</v>
       </c>
       <c r="J66">
-        <v>79.39344262</v>
+        <v>79.393442620000002</v>
       </c>
       <c r="K66" t="s">
         <v>42</v>
@@ -5717,7 +5850,7 @@
         <v>71</v>
       </c>
       <c r="S66">
-        <v>68.211268</v>
+        <v>68.211268000000004</v>
       </c>
       <c r="T66">
         <v>1.674528</v>
@@ -5729,16 +5862,16 @@
         <v>2.075472</v>
       </c>
       <c r="W66">
-        <v>55.034091</v>
+        <v>55.034090999999997</v>
       </c>
       <c r="X66">
         <v>61</v>
       </c>
       <c r="Y66">
-        <v>79.393443</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25">
+        <v>79.393443000000005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -5764,10 +5897,10 @@
         <v>3117</v>
       </c>
       <c r="I67">
-        <v>1.471607</v>
+        <v>1.4716070000000001</v>
       </c>
       <c r="J67">
-        <v>39.66942149</v>
+        <v>39.669421489999998</v>
       </c>
       <c r="K67" t="s">
         <v>42</v>
@@ -5794,7 +5927,7 @@
         <v>35.036496</v>
       </c>
       <c r="T67">
-        <v>2.986702</v>
+        <v>2.9867020000000002</v>
       </c>
       <c r="U67">
         <v>172</v>
@@ -5803,7 +5936,7 @@
         <v>3.749727</v>
       </c>
       <c r="W67">
-        <v>27.906977</v>
+        <v>27.906977000000001</v>
       </c>
       <c r="X67">
         <v>121</v>
@@ -5812,7 +5945,7 @@
         <v>39.669421</v>
       </c>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -5841,7 +5974,7 @@
         <v>1.796581</v>
       </c>
       <c r="J68">
-        <v>58.58282209</v>
+        <v>58.582822090000001</v>
       </c>
       <c r="K68" t="s">
         <v>42</v>
@@ -5859,25 +5992,25 @@
         <v>10616</v>
       </c>
       <c r="P68">
-        <v>899.491334</v>
+        <v>899.49133400000005</v>
       </c>
       <c r="Q68">
         <v>208</v>
       </c>
       <c r="S68">
-        <v>45.908654</v>
+        <v>45.908653999999999</v>
       </c>
       <c r="T68">
-        <v>1.959307</v>
+        <v>1.9593069999999999</v>
       </c>
       <c r="U68">
         <v>250</v>
       </c>
       <c r="V68">
-        <v>2.354936</v>
+        <v>2.3549359999999999</v>
       </c>
       <c r="W68">
-        <v>38.196</v>
+        <v>38.195999999999998</v>
       </c>
       <c r="X68">
         <v>163</v>
@@ -5886,7 +6019,7 @@
         <v>58.582822</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -5939,16 +6072,16 @@
         <v>139</v>
       </c>
       <c r="S69">
-        <v>34.618705</v>
+        <v>34.618704999999999</v>
       </c>
       <c r="T69">
-        <v>3.040245</v>
+        <v>3.0402450000000001</v>
       </c>
       <c r="U69">
         <v>170</v>
       </c>
       <c r="V69">
-        <v>3.718285</v>
+        <v>3.7182849999999998</v>
       </c>
       <c r="W69">
         <v>28.305882</v>
@@ -5957,10 +6090,10 @@
         <v>114</v>
       </c>
       <c r="Y69">
-        <v>42.210526</v>
-      </c>
-    </row>
-    <row r="70" spans="1:25">
+        <v>42.210526000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -5986,10 +6119,10 @@
         <v>3019</v>
       </c>
       <c r="I70">
-        <v>1.465717</v>
+        <v>1.4657169999999999</v>
       </c>
       <c r="J70">
-        <v>42.97321429</v>
+        <v>42.973214290000001</v>
       </c>
       <c r="K70" t="s">
         <v>42</v>
@@ -6013,28 +6146,28 @@
         <v>132</v>
       </c>
       <c r="S70">
-        <v>36.462121</v>
+        <v>36.462121000000003</v>
       </c>
       <c r="T70">
-        <v>2.983051</v>
+        <v>2.9830510000000001</v>
       </c>
       <c r="U70">
         <v>160</v>
       </c>
       <c r="V70">
-        <v>3.615819</v>
+        <v>3.6158190000000001</v>
       </c>
       <c r="W70">
-        <v>30.08125</v>
+        <v>30.081250000000001</v>
       </c>
       <c r="X70">
         <v>112</v>
       </c>
       <c r="Y70">
-        <v>42.973214</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25">
+        <v>42.973213999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -6060,10 +6193,10 @@
         <v>6453</v>
       </c>
       <c r="I71">
-        <v>1.229971</v>
+        <v>1.2299709999999999</v>
       </c>
       <c r="J71">
-        <v>99.66666667</v>
+        <v>99.666666669999998</v>
       </c>
       <c r="K71" t="s">
         <v>42</v>
@@ -6081,13 +6214,13 @@
         <v>7937</v>
       </c>
       <c r="P71">
-        <v>1205.493259</v>
+        <v>1205.4932590000001</v>
       </c>
       <c r="Q71">
         <v>143</v>
       </c>
       <c r="S71">
-        <v>66.909091</v>
+        <v>66.909091000000004</v>
       </c>
       <c r="T71">
         <v>1.801688</v>
@@ -6096,19 +6229,19 @@
         <v>163</v>
       </c>
       <c r="V71">
-        <v>2.053673</v>
+        <v>2.0536729999999999</v>
       </c>
       <c r="W71">
-        <v>58.699387</v>
+        <v>58.699387000000002</v>
       </c>
       <c r="X71">
         <v>96</v>
       </c>
       <c r="Y71">
-        <v>99.666667</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25">
+        <v>99.666667000000004</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -6137,7 +6270,7 @@
         <v>1.655934</v>
       </c>
       <c r="J72">
-        <v>81.31896552</v>
+        <v>81.318965520000006</v>
       </c>
       <c r="K72" t="s">
         <v>42</v>
@@ -6155,13 +6288,13 @@
         <v>9000</v>
       </c>
       <c r="P72">
-        <v>1048.111111</v>
+        <v>1048.1111109999999</v>
       </c>
       <c r="Q72">
         <v>137</v>
       </c>
       <c r="S72">
-        <v>68.854015</v>
+        <v>68.854015000000004</v>
       </c>
       <c r="T72">
         <v>1.522222</v>
@@ -6173,16 +6306,16 @@
         <v>1.888889</v>
       </c>
       <c r="W72">
-        <v>55.488235</v>
+        <v>55.488235000000003</v>
       </c>
       <c r="X72">
         <v>116</v>
       </c>
       <c r="Y72">
-        <v>81.318966</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25">
+        <v>81.318966000000003</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -6208,7 +6341,7 @@
         <v>5767</v>
       </c>
       <c r="I73">
-        <v>1.343333</v>
+        <v>1.3433330000000001</v>
       </c>
       <c r="J73">
         <v>104.61538462</v>
@@ -6229,25 +6362,25 @@
         <v>7747</v>
       </c>
       <c r="P73">
-        <v>1228.862786</v>
+        <v>1228.8627859999999</v>
       </c>
       <c r="Q73">
         <v>127</v>
       </c>
       <c r="S73">
-        <v>74.96063</v>
+        <v>74.960629999999995</v>
       </c>
       <c r="T73">
-        <v>1.639344</v>
+        <v>1.6393439999999999</v>
       </c>
       <c r="U73">
         <v>151</v>
       </c>
       <c r="V73">
-        <v>1.949142</v>
+        <v>1.9491419999999999</v>
       </c>
       <c r="W73">
-        <v>63.046358</v>
+        <v>63.046357999999998</v>
       </c>
       <c r="X73">
         <v>91</v>
@@ -6256,7 +6389,7 @@
         <v>104.615385</v>
       </c>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -6309,16 +6442,16 @@
         <v>84</v>
       </c>
       <c r="S74">
-        <v>56.452381</v>
+        <v>56.452381000000003</v>
       </c>
       <c r="T74">
-        <v>2.480071</v>
+        <v>2.4800710000000001</v>
       </c>
       <c r="U74">
         <v>100</v>
       </c>
       <c r="V74">
-        <v>2.952465</v>
+        <v>2.9524650000000001</v>
       </c>
       <c r="W74">
         <v>47.42</v>
@@ -6327,10 +6460,10 @@
         <v>75</v>
       </c>
       <c r="Y74">
-        <v>63.226667</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25">
+        <v>63.226666999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -6356,10 +6489,10 @@
         <v>2831</v>
       </c>
       <c r="I75">
-        <v>1.705758</v>
+        <v>1.7057580000000001</v>
       </c>
       <c r="J75">
-        <v>32.51724138</v>
+        <v>32.517241380000002</v>
       </c>
       <c r="K75" t="s">
         <v>42</v>
@@ -6377,22 +6510,22 @@
         <v>4829</v>
       </c>
       <c r="P75">
-        <v>976.392628</v>
+        <v>976.39262799999995</v>
       </c>
       <c r="Q75">
         <v>174</v>
       </c>
       <c r="S75">
-        <v>27.097701</v>
+        <v>27.097701000000001</v>
       </c>
       <c r="T75">
-        <v>3.60323</v>
+        <v>3.6032299999999999</v>
       </c>
       <c r="U75">
         <v>243</v>
       </c>
       <c r="V75">
-        <v>5.032098</v>
+        <v>5.0320980000000004</v>
       </c>
       <c r="W75">
         <v>19.403292</v>
@@ -6401,10 +6534,10 @@
         <v>145</v>
       </c>
       <c r="Y75">
-        <v>32.517241</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25">
+        <v>32.517240999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -6430,10 +6563,10 @@
         <v>3240</v>
       </c>
       <c r="I76">
-        <v>1.707099</v>
+        <v>1.7070989999999999</v>
       </c>
       <c r="J76">
-        <v>37.73387097</v>
+        <v>37.733870969999998</v>
       </c>
       <c r="K76" t="s">
         <v>42</v>
@@ -6451,34 +6584,34 @@
         <v>5531</v>
       </c>
       <c r="P76">
-        <v>845.959139</v>
+        <v>845.95913900000005</v>
       </c>
       <c r="Q76">
         <v>147</v>
       </c>
       <c r="S76">
-        <v>31.829932</v>
+        <v>31.829931999999999</v>
       </c>
       <c r="T76">
-        <v>2.657747</v>
+        <v>2.6577470000000001</v>
       </c>
       <c r="U76">
         <v>236</v>
       </c>
       <c r="V76">
-        <v>4.26686</v>
+        <v>4.2668600000000003</v>
       </c>
       <c r="W76">
-        <v>19.826271</v>
+        <v>19.826270999999998</v>
       </c>
       <c r="X76">
         <v>124</v>
       </c>
       <c r="Y76">
-        <v>37.733871</v>
-      </c>
-    </row>
-    <row r="77" spans="1:25">
+        <v>37.733871000000001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -6507,7 +6640,7 @@
         <v>1.063445</v>
       </c>
       <c r="J77">
-        <v>79.54761905</v>
+        <v>79.547619049999994</v>
       </c>
       <c r="K77" t="s">
         <v>42</v>
@@ -6540,7 +6673,7 @@
         <v>59</v>
       </c>
       <c r="V77">
-        <v>2.331094</v>
+        <v>2.3310940000000002</v>
       </c>
       <c r="W77">
         <v>56.627119</v>
@@ -6549,10 +6682,10 @@
         <v>42</v>
       </c>
       <c r="Y77">
-        <v>79.547619</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25">
+        <v>79.547618999999997</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -6581,7 +6714,7 @@
         <v>1.496278</v>
       </c>
       <c r="J78">
-        <v>48.56701031</v>
+        <v>48.567010310000001</v>
       </c>
       <c r="K78" t="s">
         <v>42</v>
@@ -6599,34 +6732,34 @@
         <v>4824</v>
       </c>
       <c r="P78">
-        <v>976.575456</v>
+        <v>976.57545600000003</v>
       </c>
       <c r="Q78">
         <v>125</v>
       </c>
       <c r="S78">
-        <v>37.688</v>
+        <v>37.688000000000002</v>
       </c>
       <c r="T78">
-        <v>2.591211</v>
+        <v>2.5912109999999999</v>
       </c>
       <c r="U78">
         <v>149</v>
       </c>
       <c r="V78">
-        <v>3.088723</v>
+        <v>3.0887229999999999</v>
       </c>
       <c r="W78">
-        <v>31.61745</v>
+        <v>31.617450000000002</v>
       </c>
       <c r="X78">
         <v>97</v>
       </c>
       <c r="Y78">
-        <v>48.56701</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25">
+        <v>48.567010000000003</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -6655,7 +6788,7 @@
         <v>1.33195</v>
       </c>
       <c r="J79">
-        <v>59.74683544</v>
+        <v>59.746835439999998</v>
       </c>
       <c r="K79" t="s">
         <v>42</v>
@@ -6679,7 +6812,7 @@
         <v>86</v>
       </c>
       <c r="S79">
-        <v>54.883721</v>
+        <v>54.883721000000001</v>
       </c>
       <c r="T79">
         <v>2.679128</v>
@@ -6688,19 +6821,19 @@
         <v>90</v>
       </c>
       <c r="V79">
-        <v>2.803738</v>
+        <v>2.8037380000000001</v>
       </c>
       <c r="W79">
-        <v>52.444444</v>
+        <v>52.444443999999997</v>
       </c>
       <c r="X79">
         <v>79</v>
       </c>
       <c r="Y79">
-        <v>59.746835</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25">
+        <v>59.746834999999997</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -6729,7 +6862,7 @@
         <v>1.139154</v>
       </c>
       <c r="J80">
-        <v>18.1025641</v>
+        <v>18.102564099999999</v>
       </c>
       <c r="K80" t="s">
         <v>42</v>
@@ -6747,13 +6880,13 @@
         <v>835</v>
       </c>
       <c r="P80">
-        <v>845.508982</v>
+        <v>845.50898199999995</v>
       </c>
       <c r="Q80">
         <v>40</v>
       </c>
       <c r="S80">
-        <v>17.65</v>
+        <v>17.649999999999999</v>
       </c>
       <c r="T80">
         <v>4.790419</v>
@@ -6762,7 +6895,7 @@
         <v>49</v>
       </c>
       <c r="V80">
-        <v>5.868263</v>
+        <v>5.8682629999999998</v>
       </c>
       <c r="W80">
         <v>14.408163</v>
@@ -6771,10 +6904,10 @@
         <v>39</v>
       </c>
       <c r="Y80">
-        <v>18.102564</v>
-      </c>
-    </row>
-    <row r="81" spans="1:25">
+        <v>18.102564000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -6800,10 +6933,10 @@
         <v>2931</v>
       </c>
       <c r="I81">
-        <v>1.785397</v>
+        <v>1.7853969999999999</v>
       </c>
       <c r="J81">
-        <v>53.7816092</v>
+        <v>53.781609199999998</v>
       </c>
       <c r="K81" t="s">
         <v>42</v>
@@ -6821,13 +6954,13 @@
         <v>5233</v>
       </c>
       <c r="P81">
-        <v>894.133384</v>
+        <v>894.13338399999998</v>
       </c>
       <c r="Q81">
         <v>103</v>
       </c>
       <c r="S81">
-        <v>45.427184</v>
+        <v>45.427183999999997</v>
       </c>
       <c r="T81">
         <v>1.968278</v>
@@ -6836,7 +6969,7 @@
         <v>152</v>
       </c>
       <c r="V81">
-        <v>2.904644</v>
+        <v>2.9046439999999998</v>
       </c>
       <c r="W81">
         <v>30.782895</v>
@@ -6845,10 +6978,10 @@
         <v>87</v>
       </c>
       <c r="Y81">
-        <v>53.781609</v>
-      </c>
-    </row>
-    <row r="82" spans="1:25">
+        <v>53.781609000000003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -6874,7 +7007,7 @@
         <v>2543</v>
       </c>
       <c r="I82">
-        <v>1.276838</v>
+        <v>1.2768379999999999</v>
       </c>
       <c r="J82">
         <v>32.0173913</v>
@@ -6901,16 +7034,16 @@
         <v>134</v>
       </c>
       <c r="S82">
-        <v>27.477612</v>
+        <v>27.477612000000001</v>
       </c>
       <c r="T82">
-        <v>4.126886</v>
+        <v>4.1268859999999998</v>
       </c>
       <c r="U82">
         <v>154</v>
       </c>
       <c r="V82">
-        <v>4.74284</v>
+        <v>4.7428400000000002</v>
       </c>
       <c r="W82">
         <v>23.909091</v>
@@ -6919,10 +7052,10 @@
         <v>115</v>
       </c>
       <c r="Y82">
-        <v>32.017391</v>
-      </c>
-    </row>
-    <row r="83" spans="1:25">
+        <v>32.017391000000003</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -6975,16 +7108,16 @@
         <v>76</v>
       </c>
       <c r="S83">
-        <v>47.986842</v>
+        <v>47.986842000000003</v>
       </c>
       <c r="T83">
-        <v>2.203537</v>
+        <v>2.2035369999999999</v>
       </c>
       <c r="U83">
         <v>95</v>
       </c>
       <c r="V83">
-        <v>2.754422</v>
+        <v>2.7544219999999999</v>
       </c>
       <c r="W83">
         <v>38.389474</v>
@@ -6996,7 +7129,7 @@
         <v>51.366197</v>
       </c>
     </row>
-    <row r="84" spans="1:25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -7025,7 +7158,7 @@
         <v>1.100606</v>
       </c>
       <c r="J84">
-        <v>61.26666667</v>
+        <v>61.266666669999999</v>
       </c>
       <c r="K84" t="s">
         <v>42</v>
@@ -7049,28 +7182,28 @@
         <v>68</v>
       </c>
       <c r="S84">
-        <v>54.058824</v>
+        <v>54.058824000000001</v>
       </c>
       <c r="T84">
-        <v>2.496329</v>
+        <v>2.4963289999999998</v>
       </c>
       <c r="U84">
         <v>78</v>
       </c>
       <c r="V84">
-        <v>2.863436</v>
+        <v>2.8634360000000001</v>
       </c>
       <c r="W84">
-        <v>47.128205</v>
+        <v>47.128205000000001</v>
       </c>
       <c r="X84">
         <v>60</v>
       </c>
       <c r="Y84">
-        <v>61.266667</v>
-      </c>
-    </row>
-    <row r="85" spans="1:25">
+        <v>61.266666999999998</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -7096,7 +7229,7 @@
         <v>2307</v>
       </c>
       <c r="I85">
-        <v>1.233637</v>
+        <v>1.2336370000000001</v>
       </c>
       <c r="J85">
         <v>107.20588235</v>
@@ -7123,7 +7256,7 @@
         <v>46</v>
       </c>
       <c r="S85">
-        <v>79.23913</v>
+        <v>79.239130000000003</v>
       </c>
       <c r="T85">
         <v>1.616304</v>
@@ -7135,7 +7268,7 @@
         <v>1.862263</v>
       </c>
       <c r="W85">
-        <v>68.773585</v>
+        <v>68.773584999999997</v>
       </c>
       <c r="X85">
         <v>34</v>
@@ -7144,7 +7277,7 @@
         <v>107.205882</v>
       </c>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -7170,10 +7303,10 @@
         <v>2651</v>
       </c>
       <c r="I86">
-        <v>1.314598</v>
+        <v>1.3145979999999999</v>
       </c>
       <c r="J86">
-        <v>35.90196078</v>
+        <v>35.901960780000003</v>
       </c>
       <c r="K86" t="s">
         <v>42</v>
@@ -7197,19 +7330,19 @@
         <v>113</v>
       </c>
       <c r="S86">
-        <v>32.40708</v>
+        <v>32.407080000000001</v>
       </c>
       <c r="T86">
-        <v>3.242468</v>
+        <v>3.2424680000000001</v>
       </c>
       <c r="U86">
         <v>138</v>
       </c>
       <c r="V86">
-        <v>3.959828</v>
+        <v>3.9598279999999999</v>
       </c>
       <c r="W86">
-        <v>26.536232</v>
+        <v>26.536231999999998</v>
       </c>
       <c r="X86">
         <v>102</v>
@@ -7218,7 +7351,7 @@
         <v>35.901961</v>
       </c>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -7247,7 +7380,7 @@
         <v>1.301175</v>
       </c>
       <c r="J87">
-        <v>77.40425532</v>
+        <v>77.404255320000004</v>
       </c>
       <c r="K87" t="s">
         <v>42</v>
@@ -7271,16 +7404,16 @@
         <v>54</v>
       </c>
       <c r="S87">
-        <v>67.37037</v>
+        <v>67.370369999999994</v>
       </c>
       <c r="T87">
-        <v>2.032367</v>
+        <v>2.0323669999999998</v>
       </c>
       <c r="U87">
         <v>60</v>
       </c>
       <c r="V87">
-        <v>2.258186</v>
+        <v>2.2581859999999998</v>
       </c>
       <c r="W87">
         <v>60.633333</v>
@@ -7289,10 +7422,10 @@
         <v>47</v>
       </c>
       <c r="Y87">
-        <v>77.404255</v>
-      </c>
-    </row>
-    <row r="88" spans="1:25">
+        <v>77.404255000000006</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -7318,10 +7451,10 @@
         <v>2344</v>
       </c>
       <c r="I88">
-        <v>1.149317</v>
+        <v>1.1493169999999999</v>
       </c>
       <c r="J88">
-        <v>86.71428571</v>
+        <v>86.714285709999999</v>
       </c>
       <c r="K88" t="s">
         <v>42</v>
@@ -7357,16 +7490,16 @@
         <v>1.930215</v>
       </c>
       <c r="W88">
-        <v>70.038462</v>
+        <v>70.038461999999996</v>
       </c>
       <c r="X88">
         <v>42</v>
       </c>
       <c r="Y88">
-        <v>86.714286</v>
-      </c>
-    </row>
-    <row r="89" spans="1:25">
+        <v>86.714286000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -7395,7 +7528,7 @@
         <v>1.380349</v>
       </c>
       <c r="J89">
-        <v>65.25454545</v>
+        <v>65.254545449999995</v>
       </c>
       <c r="K89" t="s">
         <v>42</v>
@@ -7413,16 +7546,16 @@
         <v>3484</v>
       </c>
       <c r="P89">
-        <v>1030.137773</v>
+        <v>1030.1377729999999</v>
       </c>
       <c r="Q89">
         <v>68</v>
       </c>
       <c r="S89">
-        <v>52.779412</v>
+        <v>52.779412000000001</v>
       </c>
       <c r="T89">
-        <v>1.95178</v>
+        <v>1.9517800000000001</v>
       </c>
       <c r="U89">
         <v>93</v>
@@ -7431,16 +7564,16 @@
         <v>2.669346</v>
       </c>
       <c r="W89">
-        <v>38.591398</v>
+        <v>38.591397999999998</v>
       </c>
       <c r="X89">
         <v>55</v>
       </c>
       <c r="Y89">
-        <v>65.254545</v>
-      </c>
-    </row>
-    <row r="90" spans="1:25">
+        <v>65.254544999999993</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -7469,7 +7602,7 @@
         <v>1.137783</v>
       </c>
       <c r="J90">
-        <v>60.31666667</v>
+        <v>60.316666669999996</v>
       </c>
       <c r="K90" t="s">
         <v>42</v>
@@ -7487,7 +7620,7 @@
         <v>2659</v>
       </c>
       <c r="P90">
-        <v>1361.037984</v>
+        <v>1361.0379840000001</v>
       </c>
       <c r="Q90">
         <v>64</v>
@@ -7496,7 +7629,7 @@
         <v>56.546875</v>
       </c>
       <c r="T90">
-        <v>2.40692</v>
+        <v>2.4069199999999999</v>
       </c>
       <c r="U90">
         <v>73</v>
@@ -7505,16 +7638,16 @@
         <v>2.745393</v>
       </c>
       <c r="W90">
-        <v>49.575342</v>
+        <v>49.575341999999999</v>
       </c>
       <c r="X90">
         <v>60</v>
       </c>
       <c r="Y90">
-        <v>60.316667</v>
-      </c>
-    </row>
-    <row r="91" spans="1:25">
+        <v>60.316667000000002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -7540,10 +7673,10 @@
         <v>2497</v>
       </c>
       <c r="I91">
-        <v>1.067281</v>
+        <v>1.0672809999999999</v>
       </c>
       <c r="J91">
-        <v>74.69387755</v>
+        <v>74.693877549999996</v>
       </c>
       <c r="K91" t="s">
         <v>42</v>
@@ -7561,7 +7694,7 @@
         <v>2665</v>
       </c>
       <c r="P91">
-        <v>1373.358349</v>
+        <v>1373.3583490000001</v>
       </c>
       <c r="Q91">
         <v>58</v>
@@ -7570,13 +7703,13 @@
         <v>63.103448</v>
       </c>
       <c r="T91">
-        <v>2.17636</v>
+        <v>2.1763599999999999</v>
       </c>
       <c r="U91">
         <v>64</v>
       </c>
       <c r="V91">
-        <v>2.401501</v>
+        <v>2.4015010000000001</v>
       </c>
       <c r="W91">
         <v>57.1875</v>
@@ -7585,10 +7718,10 @@
         <v>49</v>
       </c>
       <c r="Y91">
-        <v>74.693878</v>
-      </c>
-    </row>
-    <row r="92" spans="1:25">
+        <v>74.693877999999998</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>25</v>
       </c>
@@ -7617,7 +7750,7 @@
         <v>1.180139</v>
       </c>
       <c r="J92">
-        <v>86.64285714</v>
+        <v>86.642857140000004</v>
       </c>
       <c r="K92" t="s">
         <v>42</v>
@@ -7635,16 +7768,16 @@
         <v>2555</v>
       </c>
       <c r="P92">
-        <v>1424.266145</v>
+        <v>1424.2661450000001</v>
       </c>
       <c r="Q92">
         <v>44</v>
       </c>
       <c r="S92">
-        <v>82.704545</v>
+        <v>82.704544999999996</v>
       </c>
       <c r="T92">
-        <v>1.722114</v>
+        <v>1.7221139999999999</v>
       </c>
       <c r="U92">
         <v>50</v>
@@ -7659,10 +7792,10 @@
         <v>42</v>
       </c>
       <c r="Y92">
-        <v>86.642857</v>
-      </c>
-    </row>
-    <row r="93" spans="1:25">
+        <v>86.642857000000006</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>25</v>
       </c>
@@ -7688,10 +7821,10 @@
         <v>2852</v>
       </c>
       <c r="I93">
-        <v>1.269635</v>
+        <v>1.2696350000000001</v>
       </c>
       <c r="J93">
-        <v>28.15517241</v>
+        <v>28.155172409999999</v>
       </c>
       <c r="K93" t="s">
         <v>42</v>
@@ -7709,7 +7842,7 @@
         <v>3621</v>
       </c>
       <c r="P93">
-        <v>901.960784</v>
+        <v>901.96078399999999</v>
       </c>
       <c r="Q93">
         <v>138</v>
@@ -7724,7 +7857,7 @@
         <v>176</v>
       </c>
       <c r="V93">
-        <v>4.860536</v>
+        <v>4.8605359999999997</v>
       </c>
       <c r="W93">
         <v>18.556818</v>
@@ -7736,7 +7869,7 @@
         <v>28.155172</v>
       </c>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>25</v>
       </c>
@@ -7762,10 +7895,10 @@
         <v>1900</v>
       </c>
       <c r="I94">
-        <v>1.127368</v>
+        <v>1.1273679999999999</v>
       </c>
       <c r="J94">
-        <v>70.72340426</v>
+        <v>70.723404259999995</v>
       </c>
       <c r="K94" t="s">
         <v>42</v>
@@ -7783,7 +7916,7 @@
         <v>2142</v>
       </c>
       <c r="P94">
-        <v>1551.820728</v>
+        <v>1551.8207279999999</v>
       </c>
       <c r="Q94">
         <v>50</v>
@@ -7792,25 +7925,25 @@
         <v>66.48</v>
       </c>
       <c r="T94">
-        <v>2.334267</v>
+        <v>2.3342670000000001</v>
       </c>
       <c r="U94">
         <v>54</v>
       </c>
       <c r="V94">
-        <v>2.521008</v>
+        <v>2.5210080000000001</v>
       </c>
       <c r="W94">
-        <v>61.555556</v>
+        <v>61.555556000000003</v>
       </c>
       <c r="X94">
         <v>47</v>
       </c>
       <c r="Y94">
-        <v>70.723404</v>
-      </c>
-    </row>
-    <row r="95" spans="1:25">
+        <v>70.723404000000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>25</v>
       </c>
@@ -7836,7 +7969,7 @@
         <v>4521</v>
       </c>
       <c r="I95">
-        <v>1.267861</v>
+        <v>1.2678609999999999</v>
       </c>
       <c r="J95">
         <v>37.28846154</v>
@@ -7863,7 +7996,7 @@
         <v>182</v>
       </c>
       <c r="S95">
-        <v>31.961538</v>
+        <v>31.961538000000001</v>
       </c>
       <c r="T95">
         <v>3.175157</v>
@@ -7872,19 +8005,19 @@
         <v>247</v>
       </c>
       <c r="V95">
-        <v>4.309142</v>
+        <v>4.3091419999999996</v>
       </c>
       <c r="W95">
-        <v>23.550607</v>
+        <v>23.550606999999999</v>
       </c>
       <c r="X95">
         <v>156</v>
       </c>
       <c r="Y95">
-        <v>37.288462</v>
-      </c>
-    </row>
-    <row r="96" spans="1:25">
+        <v>37.288462000000003</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>25</v>
       </c>
@@ -7913,7 +8046,7 @@
         <v>1.106322</v>
       </c>
       <c r="J96">
-        <v>69.14705882</v>
+        <v>69.147058819999998</v>
       </c>
       <c r="K96" t="s">
         <v>42</v>
@@ -7931,34 +8064,34 @@
         <v>1540</v>
       </c>
       <c r="P96">
-        <v>1526.623377</v>
+        <v>1526.6233769999999</v>
       </c>
       <c r="Q96">
         <v>39</v>
       </c>
       <c r="S96">
-        <v>60.282051</v>
+        <v>60.282051000000003</v>
       </c>
       <c r="T96">
-        <v>2.532468</v>
+        <v>2.5324680000000002</v>
       </c>
       <c r="U96">
         <v>39</v>
       </c>
       <c r="V96">
-        <v>2.532468</v>
+        <v>2.5324680000000002</v>
       </c>
       <c r="W96">
-        <v>60.282051</v>
+        <v>60.282051000000003</v>
       </c>
       <c r="X96">
         <v>34</v>
       </c>
       <c r="Y96">
-        <v>69.147059</v>
-      </c>
-    </row>
-    <row r="97" spans="1:25">
+        <v>69.147058999999999</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -7987,7 +8120,7 @@
         <v>1.163527</v>
       </c>
       <c r="J97">
-        <v>65.84126984</v>
+        <v>65.841269839999995</v>
       </c>
       <c r="K97" t="s">
         <v>42</v>
@@ -8005,13 +8138,13 @@
         <v>2903</v>
       </c>
       <c r="P97">
-        <v>1428.86669</v>
+        <v>1428.8666900000001</v>
       </c>
       <c r="Q97">
         <v>73</v>
       </c>
       <c r="S97">
-        <v>56.821918</v>
+        <v>56.821917999999997</v>
       </c>
       <c r="T97">
         <v>2.51464</v>
@@ -8023,16 +8156,16 @@
         <v>3.100241</v>
       </c>
       <c r="W97">
-        <v>46.088889</v>
+        <v>46.088889000000002</v>
       </c>
       <c r="X97">
         <v>63</v>
       </c>
       <c r="Y97">
-        <v>65.84127</v>
-      </c>
-    </row>
-    <row r="98" spans="1:25">
+        <v>65.841269999999994</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>25</v>
       </c>
@@ -8061,7 +8194,7 @@
         <v>1.472799</v>
       </c>
       <c r="J98">
-        <v>39.58227848</v>
+        <v>39.582278479999999</v>
       </c>
       <c r="K98" t="s">
         <v>42</v>
@@ -8085,16 +8218,16 @@
         <v>96</v>
       </c>
       <c r="S98">
-        <v>32.572917</v>
+        <v>32.572916999999997</v>
       </c>
       <c r="T98">
-        <v>3.22364</v>
+        <v>3.2236400000000001</v>
       </c>
       <c r="U98">
         <v>147</v>
       </c>
       <c r="V98">
-        <v>4.936199</v>
+        <v>4.9361990000000002</v>
       </c>
       <c r="W98">
         <v>21.272109</v>
@@ -8103,10 +8236,10 @@
         <v>79</v>
       </c>
       <c r="Y98">
-        <v>39.582278</v>
-      </c>
-    </row>
-    <row r="99" spans="1:25">
+        <v>39.582278000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>25</v>
       </c>
@@ -8132,10 +8265,10 @@
         <v>8235</v>
       </c>
       <c r="I99">
-        <v>1.344869</v>
+        <v>1.3448690000000001</v>
       </c>
       <c r="J99">
-        <v>493.74522293</v>
+        <v>493.74522293000001</v>
       </c>
       <c r="K99" t="s">
         <v>42</v>
@@ -8153,16 +8286,16 @@
         <v>11075</v>
       </c>
       <c r="P99">
-        <v>6999.367946</v>
+        <v>6999.3679460000003</v>
       </c>
       <c r="Q99">
         <v>183</v>
       </c>
       <c r="S99">
-        <v>423.595628</v>
+        <v>423.59562799999998</v>
       </c>
       <c r="T99">
-        <v>1.65237</v>
+        <v>1.6523699999999999</v>
       </c>
       <c r="U99">
         <v>238</v>
@@ -8171,16 +8304,16 @@
         <v>2.148984</v>
       </c>
       <c r="W99">
-        <v>325.705882</v>
+        <v>325.70588199999997</v>
       </c>
       <c r="X99">
         <v>157</v>
       </c>
       <c r="Y99">
-        <v>493.745223</v>
-      </c>
-    </row>
-    <row r="100" spans="1:25">
+        <v>493.74522300000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>25</v>
       </c>
@@ -8227,34 +8360,34 @@
         <v>2190</v>
       </c>
       <c r="P100">
-        <v>755.251142</v>
+        <v>755.25114199999996</v>
       </c>
       <c r="Q100">
         <v>173</v>
       </c>
       <c r="S100">
-        <v>9.560694</v>
+        <v>9.5606939999999998</v>
       </c>
       <c r="T100">
-        <v>7.899543</v>
+        <v>7.8995430000000004</v>
       </c>
       <c r="U100">
         <v>217</v>
       </c>
       <c r="V100">
-        <v>9.908676</v>
+        <v>9.9086759999999998</v>
       </c>
       <c r="W100">
-        <v>7.62212</v>
+        <v>7.6221199999999998</v>
       </c>
       <c r="X100">
         <v>146</v>
       </c>
       <c r="Y100">
-        <v>11.328767</v>
-      </c>
-    </row>
-    <row r="101" spans="1:25">
+        <v>11.328766999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>25</v>
       </c>
@@ -8301,13 +8434,13 @@
         <v>1919</v>
       </c>
       <c r="P101">
-        <v>895.779052</v>
+        <v>895.77905199999998</v>
       </c>
       <c r="Q101">
         <v>58</v>
       </c>
       <c r="S101">
-        <v>29.637931</v>
+        <v>29.637930999999998</v>
       </c>
       <c r="T101">
         <v>3.022408</v>
@@ -8319,7 +8452,7 @@
         <v>3.804065</v>
       </c>
       <c r="W101">
-        <v>23.547945</v>
+        <v>23.547944999999999</v>
       </c>
       <c r="X101">
         <v>48</v>
@@ -8328,7 +8461,7 @@
         <v>35.8125</v>
       </c>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>25</v>
       </c>
@@ -8378,7 +8511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>25</v>
       </c>
@@ -8428,7 +8561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>25</v>
       </c>
@@ -8478,7 +8611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>25</v>
       </c>
@@ -8528,7 +8661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>25</v>
       </c>
@@ -8578,7 +8711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>25</v>
       </c>
@@ -8628,7 +8761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>25</v>
       </c>
@@ -8654,7 +8787,7 @@
         <v>1582</v>
       </c>
       <c r="I108">
-        <v>1.212389</v>
+        <v>1.2123889999999999</v>
       </c>
       <c r="J108">
         <v>19.65555556</v>
@@ -8675,34 +8808,34 @@
         <v>1918</v>
       </c>
       <c r="P108">
-        <v>922.314911</v>
+        <v>922.31491100000005</v>
       </c>
       <c r="Q108">
         <v>109</v>
       </c>
       <c r="S108">
-        <v>16.229358</v>
+        <v>16.229358000000001</v>
       </c>
       <c r="T108">
-        <v>5.683003</v>
+        <v>5.6830030000000002</v>
       </c>
       <c r="U108">
         <v>150</v>
       </c>
       <c r="V108">
-        <v>7.820647</v>
+        <v>7.8206470000000001</v>
       </c>
       <c r="W108">
-        <v>11.793333</v>
+        <v>11.793333000000001</v>
       </c>
       <c r="X108">
         <v>90</v>
       </c>
       <c r="Y108">
-        <v>19.655556</v>
-      </c>
-    </row>
-    <row r="109" spans="1:25">
+        <v>19.655556000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>25</v>
       </c>
@@ -8731,7 +8864,7 @@
         <v>1.079779</v>
       </c>
       <c r="J109">
-        <v>140.78571429</v>
+        <v>140.78571428999999</v>
       </c>
       <c r="K109" t="s">
         <v>42</v>
@@ -8758,7 +8891,7 @@
         <v>109.5</v>
       </c>
       <c r="T109">
-        <v>1.316752</v>
+        <v>1.3167519999999999</v>
       </c>
       <c r="U109">
         <v>21</v>
@@ -8767,16 +8900,16 @@
         <v>1.536211</v>
       </c>
       <c r="W109">
-        <v>93.857143</v>
+        <v>93.857142999999994</v>
       </c>
       <c r="X109">
         <v>14</v>
       </c>
       <c r="Y109">
-        <v>140.785714</v>
-      </c>
-    </row>
-    <row r="110" spans="1:25">
+        <v>140.78571400000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>25</v>
       </c>
@@ -8802,7 +8935,7 @@
         <v>1875</v>
       </c>
       <c r="I110">
-        <v>1.1984</v>
+        <v>1.1983999999999999</v>
       </c>
       <c r="J110">
         <v>26.49206349</v>
@@ -8823,34 +8956,34 @@
         <v>2247</v>
       </c>
       <c r="P110">
-        <v>742.768135</v>
+        <v>742.76813500000003</v>
       </c>
       <c r="Q110">
         <v>74</v>
       </c>
       <c r="S110">
-        <v>22.554054</v>
+        <v>22.554054000000001</v>
       </c>
       <c r="T110">
-        <v>3.29328</v>
+        <v>3.2932800000000002</v>
       </c>
       <c r="U110">
         <v>85</v>
       </c>
       <c r="V110">
-        <v>3.782822</v>
+        <v>3.7828219999999999</v>
       </c>
       <c r="W110">
-        <v>19.635294</v>
+        <v>19.635293999999998</v>
       </c>
       <c r="X110">
         <v>63</v>
       </c>
       <c r="Y110">
-        <v>26.492063</v>
-      </c>
-    </row>
-    <row r="111" spans="1:25">
+        <v>26.492063000000002</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>25</v>
       </c>
@@ -8900,7 +9033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>25</v>
       </c>
@@ -8929,7 +9062,7 @@
         <v>1.061069</v>
       </c>
       <c r="J112">
-        <v>17.52631579</v>
+        <v>17.526315790000002</v>
       </c>
       <c r="K112" t="s">
         <v>42</v>
@@ -8953,7 +9086,7 @@
         <v>21</v>
       </c>
       <c r="S112">
-        <v>15.857143</v>
+        <v>15.857143000000001</v>
       </c>
       <c r="T112">
         <v>5.035971</v>
@@ -8962,7 +9095,7 @@
         <v>32</v>
       </c>
       <c r="V112">
-        <v>7.673861</v>
+        <v>7.6738609999999996</v>
       </c>
       <c r="W112">
         <v>10.40625</v>
@@ -8971,10 +9104,10 @@
         <v>19</v>
       </c>
       <c r="Y112">
-        <v>17.526316</v>
-      </c>
-    </row>
-    <row r="113" spans="1:25">
+        <v>17.526316000000001</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>25</v>
       </c>
@@ -9027,16 +9160,16 @@
         <v>11</v>
       </c>
       <c r="S113">
-        <v>33.272727</v>
+        <v>33.272727000000003</v>
       </c>
       <c r="T113">
-        <v>3.293413</v>
+        <v>3.2934130000000001</v>
       </c>
       <c r="U113">
         <v>12</v>
       </c>
       <c r="V113">
-        <v>3.592814</v>
+        <v>3.5928140000000002</v>
       </c>
       <c r="W113">
         <v>30.5</v>
@@ -9048,7 +9181,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>25</v>
       </c>
@@ -9074,7 +9207,7 @@
         <v>489</v>
       </c>
       <c r="I114">
-        <v>1.02863</v>
+        <v>1.0286299999999999</v>
       </c>
       <c r="J114">
         <v>123.6</v>
@@ -9095,22 +9228,22 @@
         <v>503</v>
       </c>
       <c r="P114">
-        <v>1228.628231</v>
+        <v>1228.6282309999999</v>
       </c>
       <c r="Q114">
         <v>7</v>
       </c>
       <c r="S114">
-        <v>88.285714</v>
+        <v>88.285713999999999</v>
       </c>
       <c r="T114">
-        <v>1.39165</v>
+        <v>1.3916500000000001</v>
       </c>
       <c r="U114">
         <v>10</v>
       </c>
       <c r="V114">
-        <v>1.988072</v>
+        <v>1.9880720000000001</v>
       </c>
       <c r="W114">
         <v>61.8</v>
@@ -9122,7 +9255,7 @@
         <v>123.6</v>
       </c>
     </row>
-    <row r="115" spans="1:25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>25</v>
       </c>
@@ -9148,7 +9281,7 @@
         <v>314</v>
       </c>
       <c r="I115">
-        <v>1.066879</v>
+        <v>1.0668789999999999</v>
       </c>
       <c r="J115">
         <v>76.625</v>
@@ -9169,7 +9302,7 @@
         <v>335</v>
       </c>
       <c r="P115">
-        <v>1829.850746</v>
+        <v>1829.8507460000001</v>
       </c>
       <c r="Q115">
         <v>10</v>
@@ -9178,13 +9311,13 @@
         <v>61.3</v>
       </c>
       <c r="T115">
-        <v>2.985075</v>
+        <v>2.9850750000000001</v>
       </c>
       <c r="U115">
         <v>10</v>
       </c>
       <c r="V115">
-        <v>2.985075</v>
+        <v>2.9850750000000001</v>
       </c>
       <c r="W115">
         <v>61.3</v>
@@ -9196,7 +9329,7 @@
         <v>76.625</v>
       </c>
     </row>
-    <row r="116" spans="1:25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>25</v>
       </c>
@@ -9252,13 +9385,13 @@
         <v>38.8125</v>
       </c>
       <c r="T116">
-        <v>3.448276</v>
+        <v>3.4482759999999999</v>
       </c>
       <c r="U116">
         <v>27</v>
       </c>
       <c r="V116">
-        <v>5.818966</v>
+        <v>5.8189659999999996</v>
       </c>
       <c r="W116">
         <v>23</v>
@@ -9267,10 +9400,10 @@
         <v>13</v>
       </c>
       <c r="Y116">
-        <v>47.769231</v>
-      </c>
-    </row>
-    <row r="117" spans="1:25">
+        <v>47.769230999999998</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>25</v>
       </c>
@@ -9299,7 +9432,7 @@
         <v>1.240067</v>
       </c>
       <c r="J117">
-        <v>98.44420601</v>
+        <v>98.444206010000002</v>
       </c>
       <c r="K117" t="s">
         <v>42</v>
@@ -9323,28 +9456,28 @@
         <v>1178</v>
       </c>
       <c r="S117">
-        <v>77.886248</v>
+        <v>77.886247999999995</v>
       </c>
       <c r="T117">
-        <v>1.890032</v>
+        <v>1.8900319999999999</v>
       </c>
       <c r="U117">
         <v>1305</v>
       </c>
       <c r="V117">
-        <v>2.093796</v>
+        <v>2.0937960000000002</v>
       </c>
       <c r="W117">
-        <v>70.306513</v>
+        <v>70.306512999999995</v>
       </c>
       <c r="X117">
         <v>932</v>
       </c>
       <c r="Y117">
-        <v>98.444206</v>
-      </c>
-    </row>
-    <row r="118" spans="1:25">
+        <v>98.444205999999994</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>25</v>
       </c>
@@ -9373,7 +9506,7 @@
         <v>1</v>
       </c>
       <c r="J118">
-        <v>70.16666667</v>
+        <v>70.166666669999998</v>
       </c>
       <c r="K118" t="s">
         <v>42</v>
@@ -9397,10 +9530,10 @@
         <v>7</v>
       </c>
       <c r="S118">
-        <v>60.142857</v>
+        <v>60.142856999999999</v>
       </c>
       <c r="T118">
-        <v>2.167183</v>
+        <v>2.1671830000000001</v>
       </c>
       <c r="U118">
         <v>9</v>
@@ -9409,16 +9542,16 @@
         <v>2.786378</v>
       </c>
       <c r="W118">
-        <v>46.777778</v>
+        <v>46.777777999999998</v>
       </c>
       <c r="X118">
         <v>6</v>
       </c>
       <c r="Y118">
-        <v>70.166667</v>
-      </c>
-    </row>
-    <row r="119" spans="1:25">
+        <v>70.166667000000004</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>25</v>
       </c>
@@ -9456,7 +9589,7 @@
         <v>98</v>
       </c>
       <c r="P119">
-        <v>979.591837</v>
+        <v>979.59183700000006</v>
       </c>
       <c r="U119">
         <v>0</v>
@@ -9468,18 +9601,2207 @@
         <v>0</v>
       </c>
     </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B120" t="s">
+        <v>26</v>
+      </c>
+      <c r="C120" t="s">
+        <v>235</v>
+      </c>
+      <c r="D120" t="s">
+        <v>28</v>
+      </c>
+      <c r="E120" t="s">
+        <v>29</v>
+      </c>
+      <c r="F120">
+        <v>25</v>
+      </c>
+      <c r="G120" t="s">
+        <v>41</v>
+      </c>
+      <c r="H120">
+        <v>3624</v>
+      </c>
+      <c r="I120">
+        <v>1.416391</v>
+      </c>
+      <c r="J120">
+        <v>182.88</v>
+      </c>
+      <c r="K120" t="s">
+        <v>42</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>4572</v>
+      </c>
+      <c r="N120" t="s">
+        <v>54</v>
+      </c>
+      <c r="O120">
+        <v>5133</v>
+      </c>
+      <c r="P120">
+        <v>890.70718899999997</v>
+      </c>
+      <c r="Q120">
+        <v>54</v>
+      </c>
+      <c r="S120">
+        <v>84.666667000000004</v>
+      </c>
+      <c r="T120">
+        <v>1.0520160000000001</v>
+      </c>
+      <c r="U120">
+        <v>62</v>
+      </c>
+      <c r="V120">
+        <v>1.2078709999999999</v>
+      </c>
+      <c r="W120">
+        <v>73.741934999999998</v>
+      </c>
+      <c r="X120">
+        <v>25</v>
+      </c>
+      <c r="Y120">
+        <v>182.88</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" t="s">
+        <v>234</v>
+      </c>
+      <c r="D121" t="s">
+        <v>194</v>
+      </c>
+      <c r="E121" t="s">
+        <v>29</v>
+      </c>
+      <c r="F121">
+        <v>62</v>
+      </c>
+      <c r="G121" t="s">
+        <v>30</v>
+      </c>
+      <c r="H121">
+        <v>1495</v>
+      </c>
+      <c r="I121">
+        <v>1.101003</v>
+      </c>
+      <c r="J121">
+        <v>35.612903230000001</v>
+      </c>
+      <c r="K121" t="s">
+        <v>42</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>2208</v>
+      </c>
+      <c r="N121" t="s">
+        <v>233</v>
+      </c>
+      <c r="O121">
+        <v>1646</v>
+      </c>
+      <c r="P121">
+        <v>1341.433779</v>
+      </c>
+      <c r="Q121">
+        <v>62</v>
+      </c>
+      <c r="S121">
+        <v>35.612903000000003</v>
+      </c>
+      <c r="T121">
+        <v>3.7667069999999998</v>
+      </c>
+      <c r="U121">
+        <v>59</v>
+      </c>
+      <c r="V121">
+        <v>3.5844469999999999</v>
+      </c>
+      <c r="W121">
+        <v>37.423729000000002</v>
+      </c>
+      <c r="X121">
+        <v>52</v>
+      </c>
+      <c r="Y121">
+        <v>42.461537999999997</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>25</v>
+      </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" t="s">
+        <v>232</v>
+      </c>
+      <c r="D122" t="s">
+        <v>194</v>
+      </c>
+      <c r="E122" t="s">
+        <v>29</v>
+      </c>
+      <c r="F122">
+        <v>27</v>
+      </c>
+      <c r="G122" t="s">
+        <v>41</v>
+      </c>
+      <c r="H122">
+        <v>1862</v>
+      </c>
+      <c r="I122">
+        <v>1.1052630000000001</v>
+      </c>
+      <c r="J122">
+        <v>93.333333330000002</v>
+      </c>
+      <c r="K122" t="s">
+        <v>42</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>2520</v>
+      </c>
+      <c r="N122" t="s">
+        <v>228</v>
+      </c>
+      <c r="O122">
+        <v>2058</v>
+      </c>
+      <c r="P122">
+        <v>1224.4897960000001</v>
+      </c>
+      <c r="Q122">
+        <v>30</v>
+      </c>
+      <c r="S122">
+        <v>84</v>
+      </c>
+      <c r="T122">
+        <v>1.4577260000000001</v>
+      </c>
+      <c r="U122">
+        <v>32</v>
+      </c>
+      <c r="V122">
+        <v>1.554908</v>
+      </c>
+      <c r="W122">
+        <v>78.75</v>
+      </c>
+      <c r="X122">
+        <v>27</v>
+      </c>
+      <c r="Y122">
+        <v>93.333332999999996</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" t="s">
+        <v>231</v>
+      </c>
+      <c r="D123" t="s">
+        <v>194</v>
+      </c>
+      <c r="E123" t="s">
+        <v>29</v>
+      </c>
+      <c r="F123">
+        <v>44</v>
+      </c>
+      <c r="G123" t="s">
+        <v>30</v>
+      </c>
+      <c r="H123">
+        <v>3304</v>
+      </c>
+      <c r="I123">
+        <v>1.1401330000000001</v>
+      </c>
+      <c r="J123">
+        <v>79.204545449999998</v>
+      </c>
+      <c r="K123" t="s">
+        <v>42</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>3485</v>
+      </c>
+      <c r="N123" t="s">
+        <v>218</v>
+      </c>
+      <c r="O123">
+        <v>3767</v>
+      </c>
+      <c r="P123">
+        <v>925.13936799999999</v>
+      </c>
+      <c r="Q123">
+        <v>44</v>
+      </c>
+      <c r="S123">
+        <v>79.204544999999996</v>
+      </c>
+      <c r="T123">
+        <v>1.1680379999999999</v>
+      </c>
+      <c r="U123">
+        <v>47</v>
+      </c>
+      <c r="V123">
+        <v>1.2476769999999999</v>
+      </c>
+      <c r="W123">
+        <v>74.148936000000006</v>
+      </c>
+      <c r="X123">
+        <v>36</v>
+      </c>
+      <c r="Y123">
+        <v>96.805555999999996</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>25</v>
+      </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" t="s">
+        <v>230</v>
+      </c>
+      <c r="D124" t="s">
+        <v>28</v>
+      </c>
+      <c r="E124" t="s">
+        <v>29</v>
+      </c>
+      <c r="F124">
+        <v>38</v>
+      </c>
+      <c r="G124" t="s">
+        <v>41</v>
+      </c>
+      <c r="H124">
+        <v>3350</v>
+      </c>
+      <c r="I124">
+        <v>1.219104</v>
+      </c>
+      <c r="J124">
+        <v>129.92105262999999</v>
+      </c>
+      <c r="K124" t="s">
+        <v>42</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>4937</v>
+      </c>
+      <c r="N124" t="s">
+        <v>62</v>
+      </c>
+      <c r="O124">
+        <v>4084</v>
+      </c>
+      <c r="P124">
+        <v>1208.863859</v>
+      </c>
+      <c r="Q124">
+        <v>88</v>
+      </c>
+      <c r="S124">
+        <v>56.102272999999997</v>
+      </c>
+      <c r="T124">
+        <v>2.1547499999999999</v>
+      </c>
+      <c r="U124">
+        <v>104</v>
+      </c>
+      <c r="V124">
+        <v>2.5465230000000001</v>
+      </c>
+      <c r="W124">
+        <v>47.471153999999999</v>
+      </c>
+      <c r="X124">
+        <v>38</v>
+      </c>
+      <c r="Y124">
+        <v>129.921053</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>25</v>
+      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" t="s">
+        <v>229</v>
+      </c>
+      <c r="D125" t="s">
+        <v>102</v>
+      </c>
+      <c r="E125" t="s">
+        <v>29</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="K125" t="s">
+        <v>42</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125" t="s">
+        <v>228</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="U125">
+        <v>0</v>
+      </c>
+      <c r="V125">
+        <v>0</v>
+      </c>
+      <c r="W125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" t="s">
+        <v>227</v>
+      </c>
+      <c r="D126" t="s">
+        <v>28</v>
+      </c>
+      <c r="E126" t="s">
+        <v>29</v>
+      </c>
+      <c r="F126">
+        <v>95</v>
+      </c>
+      <c r="G126" t="s">
+        <v>41</v>
+      </c>
+      <c r="H126">
+        <v>2566</v>
+      </c>
+      <c r="I126">
+        <v>1.2646139999999999</v>
+      </c>
+      <c r="J126">
+        <v>51</v>
+      </c>
+      <c r="K126" t="s">
+        <v>42</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>4845</v>
+      </c>
+      <c r="N126" t="s">
+        <v>60</v>
+      </c>
+      <c r="O126">
+        <v>3245</v>
+      </c>
+      <c r="P126">
+        <v>1493.0662560000001</v>
+      </c>
+      <c r="Q126">
+        <v>99</v>
+      </c>
+      <c r="S126">
+        <v>48.939394</v>
+      </c>
+      <c r="T126">
+        <v>3.0508470000000001</v>
+      </c>
+      <c r="U126">
+        <v>109</v>
+      </c>
+      <c r="V126">
+        <v>3.3590140000000002</v>
+      </c>
+      <c r="W126">
+        <v>44.449541000000004</v>
+      </c>
+      <c r="X126">
+        <v>95</v>
+      </c>
+      <c r="Y126">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" t="s">
+        <v>226</v>
+      </c>
+      <c r="D127" t="s">
+        <v>28</v>
+      </c>
+      <c r="E127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F127">
+        <v>422</v>
+      </c>
+      <c r="G127" t="s">
+        <v>41</v>
+      </c>
+      <c r="H127">
+        <v>8270</v>
+      </c>
+      <c r="I127">
+        <v>1.516445</v>
+      </c>
+      <c r="J127">
+        <v>52.26540284</v>
+      </c>
+      <c r="K127" t="s">
+        <v>42</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>22056</v>
+      </c>
+      <c r="N127" t="s">
+        <v>225</v>
+      </c>
+      <c r="O127">
+        <v>12541</v>
+      </c>
+      <c r="P127">
+        <v>1758.711427</v>
+      </c>
+      <c r="Q127">
+        <v>451</v>
+      </c>
+      <c r="S127">
+        <v>48.904656000000003</v>
+      </c>
+      <c r="T127">
+        <v>3.5962040000000002</v>
+      </c>
+      <c r="U127">
+        <v>522</v>
+      </c>
+      <c r="V127">
+        <v>4.1623479999999997</v>
+      </c>
+      <c r="W127">
+        <v>42.252873999999998</v>
+      </c>
+      <c r="X127">
+        <v>422</v>
+      </c>
+      <c r="Y127">
+        <v>52.265402999999999</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>25</v>
+      </c>
+      <c r="B128" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" t="s">
+        <v>224</v>
+      </c>
+      <c r="D128" t="s">
+        <v>102</v>
+      </c>
+      <c r="E128" t="s">
+        <v>29</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="K128" t="s">
+        <v>42</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128" t="s">
+        <v>192</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="U128">
+        <v>0</v>
+      </c>
+      <c r="V128">
+        <v>0</v>
+      </c>
+      <c r="W128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="B129" t="s">
+        <v>26</v>
+      </c>
+      <c r="C129" t="s">
+        <v>223</v>
+      </c>
+      <c r="D129" t="s">
+        <v>28</v>
+      </c>
+      <c r="E129" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129">
+        <v>85</v>
+      </c>
+      <c r="G129" t="s">
+        <v>41</v>
+      </c>
+      <c r="H129">
+        <v>3471</v>
+      </c>
+      <c r="I129">
+        <v>1.226736</v>
+      </c>
+      <c r="J129">
+        <v>55.388235289999997</v>
+      </c>
+      <c r="K129" t="s">
+        <v>42</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>4708</v>
+      </c>
+      <c r="N129" t="s">
+        <v>222</v>
+      </c>
+      <c r="O129">
+        <v>4258</v>
+      </c>
+      <c r="P129">
+        <v>1105.683419</v>
+      </c>
+      <c r="Q129">
+        <v>114</v>
+      </c>
+      <c r="S129">
+        <v>41.298245999999999</v>
+      </c>
+      <c r="T129">
+        <v>2.6773129999999998</v>
+      </c>
+      <c r="U129">
+        <v>128</v>
+      </c>
+      <c r="V129">
+        <v>3.0061059999999999</v>
+      </c>
+      <c r="W129">
+        <v>36.78125</v>
+      </c>
+      <c r="X129">
+        <v>85</v>
+      </c>
+      <c r="Y129">
+        <v>55.388235000000002</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B130" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" t="s">
+        <v>221</v>
+      </c>
+      <c r="D130" t="s">
+        <v>28</v>
+      </c>
+      <c r="E130" t="s">
+        <v>29</v>
+      </c>
+      <c r="F130">
+        <v>100</v>
+      </c>
+      <c r="G130" t="s">
+        <v>30</v>
+      </c>
+      <c r="H130">
+        <v>3439</v>
+      </c>
+      <c r="I130">
+        <v>1.2649030000000001</v>
+      </c>
+      <c r="J130">
+        <v>45.28</v>
+      </c>
+      <c r="K130" t="s">
+        <v>42</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>4528</v>
+      </c>
+      <c r="N130" t="s">
+        <v>220</v>
+      </c>
+      <c r="O130">
+        <v>4350</v>
+      </c>
+      <c r="P130">
+        <v>1040.9195400000001</v>
+      </c>
+      <c r="Q130">
+        <v>100</v>
+      </c>
+      <c r="S130">
+        <v>45.28</v>
+      </c>
+      <c r="T130">
+        <v>2.298851</v>
+      </c>
+      <c r="U130">
+        <v>118</v>
+      </c>
+      <c r="V130">
+        <v>2.7126440000000001</v>
+      </c>
+      <c r="W130">
+        <v>38.372881</v>
+      </c>
+      <c r="X130">
+        <v>81</v>
+      </c>
+      <c r="Y130">
+        <v>55.901235</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" t="s">
+        <v>219</v>
+      </c>
+      <c r="D131" t="s">
+        <v>194</v>
+      </c>
+      <c r="E131" t="s">
+        <v>29</v>
+      </c>
+      <c r="F131">
+        <v>81</v>
+      </c>
+      <c r="G131" t="s">
+        <v>30</v>
+      </c>
+      <c r="H131">
+        <v>2038</v>
+      </c>
+      <c r="I131">
+        <v>1.080962</v>
+      </c>
+      <c r="J131">
+        <v>34.641975309999999</v>
+      </c>
+      <c r="K131" t="s">
+        <v>42</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>2806</v>
+      </c>
+      <c r="N131" t="s">
+        <v>218</v>
+      </c>
+      <c r="O131">
+        <v>2203</v>
+      </c>
+      <c r="P131">
+        <v>1273.717658</v>
+      </c>
+      <c r="Q131">
+        <v>81</v>
+      </c>
+      <c r="S131">
+        <v>34.641975000000002</v>
+      </c>
+      <c r="T131">
+        <v>3.6768040000000002</v>
+      </c>
+      <c r="U131">
+        <v>98</v>
+      </c>
+      <c r="V131">
+        <v>4.4484789999999998</v>
+      </c>
+      <c r="W131">
+        <v>28.632653000000001</v>
+      </c>
+      <c r="X131">
+        <v>59</v>
+      </c>
+      <c r="Y131">
+        <v>47.559322000000002</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" t="s">
+        <v>217</v>
+      </c>
+      <c r="D132" t="s">
+        <v>194</v>
+      </c>
+      <c r="E132" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132">
+        <v>73</v>
+      </c>
+      <c r="G132" t="s">
+        <v>30</v>
+      </c>
+      <c r="H132">
+        <v>1286</v>
+      </c>
+      <c r="I132">
+        <v>1.0715399999999999</v>
+      </c>
+      <c r="J132">
+        <v>35.150684929999997</v>
+      </c>
+      <c r="K132" t="s">
+        <v>42</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>2566</v>
+      </c>
+      <c r="N132" t="s">
+        <v>205</v>
+      </c>
+      <c r="O132">
+        <v>1378</v>
+      </c>
+      <c r="P132">
+        <v>1862.119013</v>
+      </c>
+      <c r="Q132">
+        <v>73</v>
+      </c>
+      <c r="S132">
+        <v>35.150685000000003</v>
+      </c>
+      <c r="T132">
+        <v>5.2975329999999996</v>
+      </c>
+      <c r="U132">
+        <v>76</v>
+      </c>
+      <c r="V132">
+        <v>5.5152390000000002</v>
+      </c>
+      <c r="W132">
+        <v>33.763157999999997</v>
+      </c>
+      <c r="X132">
+        <v>57</v>
+      </c>
+      <c r="Y132">
+        <v>45.017544000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>25</v>
+      </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" t="s">
+        <v>216</v>
+      </c>
+      <c r="D133" t="s">
+        <v>28</v>
+      </c>
+      <c r="E133" t="s">
+        <v>29</v>
+      </c>
+      <c r="F133">
+        <v>52</v>
+      </c>
+      <c r="G133" t="s">
+        <v>30</v>
+      </c>
+      <c r="H133">
+        <v>3555</v>
+      </c>
+      <c r="I133">
+        <v>1.1952179999999999</v>
+      </c>
+      <c r="J133">
+        <v>79.32692308</v>
+      </c>
+      <c r="K133" t="s">
+        <v>42</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>4125</v>
+      </c>
+      <c r="N133" t="s">
+        <v>215</v>
+      </c>
+      <c r="O133">
+        <v>4249</v>
+      </c>
+      <c r="P133">
+        <v>970.81666299999995</v>
+      </c>
+      <c r="Q133">
+        <v>52</v>
+      </c>
+      <c r="S133">
+        <v>79.326922999999994</v>
+      </c>
+      <c r="T133">
+        <v>1.2238169999999999</v>
+      </c>
+      <c r="U133">
+        <v>53</v>
+      </c>
+      <c r="V133">
+        <v>1.247352</v>
+      </c>
+      <c r="W133">
+        <v>77.830189000000004</v>
+      </c>
+      <c r="X133">
+        <v>26</v>
+      </c>
+      <c r="Y133">
+        <v>158.65384599999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>25</v>
+      </c>
+      <c r="B134" t="s">
+        <v>26</v>
+      </c>
+      <c r="C134" t="s">
+        <v>214</v>
+      </c>
+      <c r="D134" t="s">
+        <v>194</v>
+      </c>
+      <c r="E134" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134">
+        <v>88</v>
+      </c>
+      <c r="G134" t="s">
+        <v>30</v>
+      </c>
+      <c r="H134">
+        <v>1599</v>
+      </c>
+      <c r="I134">
+        <v>1.101313</v>
+      </c>
+      <c r="J134">
+        <v>31.329545450000001</v>
+      </c>
+      <c r="K134" t="s">
+        <v>42</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>2757</v>
+      </c>
+      <c r="N134" t="s">
+        <v>196</v>
+      </c>
+      <c r="O134">
+        <v>1761</v>
+      </c>
+      <c r="P134">
+        <v>1565.587734</v>
+      </c>
+      <c r="Q134">
+        <v>88</v>
+      </c>
+      <c r="S134">
+        <v>31.329545</v>
+      </c>
+      <c r="T134">
+        <v>4.9971610000000002</v>
+      </c>
+      <c r="U134">
+        <v>90</v>
+      </c>
+      <c r="V134">
+        <v>5.1107329999999997</v>
+      </c>
+      <c r="W134">
+        <v>30.633333</v>
+      </c>
+      <c r="X134">
+        <v>63</v>
+      </c>
+      <c r="Y134">
+        <v>43.761904999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>25</v>
+      </c>
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" t="s">
+        <v>213</v>
+      </c>
+      <c r="D135" t="s">
+        <v>28</v>
+      </c>
+      <c r="E135" t="s">
+        <v>29</v>
+      </c>
+      <c r="F135">
+        <v>151</v>
+      </c>
+      <c r="G135" t="s">
+        <v>30</v>
+      </c>
+      <c r="H135">
+        <v>3235</v>
+      </c>
+      <c r="I135">
+        <v>1.2516229999999999</v>
+      </c>
+      <c r="J135">
+        <v>28.90066225</v>
+      </c>
+      <c r="K135" t="s">
+        <v>42</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>4364</v>
+      </c>
+      <c r="N135" t="s">
+        <v>212</v>
+      </c>
+      <c r="O135">
+        <v>4049</v>
+      </c>
+      <c r="P135">
+        <v>1077.7969869999999</v>
+      </c>
+      <c r="Q135">
+        <v>151</v>
+      </c>
+      <c r="S135">
+        <v>28.900662000000001</v>
+      </c>
+      <c r="T135">
+        <v>3.7293159999999999</v>
+      </c>
+      <c r="U135">
+        <v>163</v>
+      </c>
+      <c r="V135">
+        <v>4.0256850000000002</v>
+      </c>
+      <c r="W135">
+        <v>26.773005999999999</v>
+      </c>
+      <c r="X135">
+        <v>126</v>
+      </c>
+      <c r="Y135">
+        <v>34.634920999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="B136" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136" t="s">
+        <v>211</v>
+      </c>
+      <c r="D136" t="s">
+        <v>28</v>
+      </c>
+      <c r="E136" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136">
+        <v>187</v>
+      </c>
+      <c r="G136" t="s">
+        <v>41</v>
+      </c>
+      <c r="H136">
+        <v>4039</v>
+      </c>
+      <c r="I136">
+        <v>1.4196580000000001</v>
+      </c>
+      <c r="J136">
+        <v>30.513368979999999</v>
+      </c>
+      <c r="K136" t="s">
+        <v>42</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>5706</v>
+      </c>
+      <c r="N136" t="s">
+        <v>70</v>
+      </c>
+      <c r="O136">
+        <v>5734</v>
+      </c>
+      <c r="P136">
+        <v>995.11684700000001</v>
+      </c>
+      <c r="Q136">
+        <v>215</v>
+      </c>
+      <c r="S136">
+        <v>26.539535000000001</v>
+      </c>
+      <c r="T136">
+        <v>3.7495639999999999</v>
+      </c>
+      <c r="U136">
+        <v>271</v>
+      </c>
+      <c r="V136">
+        <v>4.7261949999999997</v>
+      </c>
+      <c r="W136">
+        <v>21.055351000000002</v>
+      </c>
+      <c r="X136">
+        <v>187</v>
+      </c>
+      <c r="Y136">
+        <v>30.513369000000001</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>25</v>
+      </c>
+      <c r="B137" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" t="s">
+        <v>210</v>
+      </c>
+      <c r="D137" t="s">
+        <v>194</v>
+      </c>
+      <c r="E137" t="s">
+        <v>29</v>
+      </c>
+      <c r="F137">
+        <v>67</v>
+      </c>
+      <c r="G137" t="s">
+        <v>30</v>
+      </c>
+      <c r="H137">
+        <v>1830</v>
+      </c>
+      <c r="I137">
+        <v>1.20929</v>
+      </c>
+      <c r="J137">
+        <v>42.074626870000003</v>
+      </c>
+      <c r="K137" t="s">
+        <v>42</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>2819</v>
+      </c>
+      <c r="N137" t="s">
+        <v>205</v>
+      </c>
+      <c r="O137">
+        <v>2213</v>
+      </c>
+      <c r="P137">
+        <v>1273.836421</v>
+      </c>
+      <c r="Q137">
+        <v>67</v>
+      </c>
+      <c r="S137">
+        <v>42.074627</v>
+      </c>
+      <c r="T137">
+        <v>3.0275639999999999</v>
+      </c>
+      <c r="U137">
+        <v>79</v>
+      </c>
+      <c r="V137">
+        <v>3.5698150000000002</v>
+      </c>
+      <c r="W137">
+        <v>35.683543999999998</v>
+      </c>
+      <c r="X137">
+        <v>51</v>
+      </c>
+      <c r="Y137">
+        <v>55.274509999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>25</v>
+      </c>
+      <c r="B138" t="s">
+        <v>26</v>
+      </c>
+      <c r="C138" t="s">
+        <v>84</v>
+      </c>
+      <c r="D138" t="s">
+        <v>102</v>
+      </c>
+      <c r="E138" t="s">
+        <v>29</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="K138" t="s">
+        <v>42</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138" t="s">
+        <v>209</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>25</v>
+      </c>
+      <c r="B139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" t="s">
+        <v>208</v>
+      </c>
+      <c r="D139" t="s">
+        <v>102</v>
+      </c>
+      <c r="E139" t="s">
+        <v>29</v>
+      </c>
+      <c r="F139">
+        <v>97</v>
+      </c>
+      <c r="G139" t="s">
+        <v>41</v>
+      </c>
+      <c r="H139">
+        <v>4075</v>
+      </c>
+      <c r="I139">
+        <v>1.2019629999999999</v>
+      </c>
+      <c r="J139">
+        <v>58.340206190000004</v>
+      </c>
+      <c r="K139" t="s">
+        <v>42</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>5659</v>
+      </c>
+      <c r="N139" t="s">
+        <v>74</v>
+      </c>
+      <c r="O139">
+        <v>4898</v>
+      </c>
+      <c r="P139">
+        <v>1155.369539</v>
+      </c>
+      <c r="Q139">
+        <v>118</v>
+      </c>
+      <c r="S139">
+        <v>47.957627000000002</v>
+      </c>
+      <c r="T139">
+        <v>2.4091469999999999</v>
+      </c>
+      <c r="U139">
+        <v>147</v>
+      </c>
+      <c r="V139">
+        <v>3.0012249999999998</v>
+      </c>
+      <c r="W139">
+        <v>38.496599000000003</v>
+      </c>
+      <c r="X139">
+        <v>97</v>
+      </c>
+      <c r="Y139">
+        <v>58.340206000000002</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>25</v>
+      </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140" t="s">
+        <v>207</v>
+      </c>
+      <c r="D140" t="s">
+        <v>194</v>
+      </c>
+      <c r="E140" t="s">
+        <v>29</v>
+      </c>
+      <c r="F140">
+        <v>49</v>
+      </c>
+      <c r="G140" t="s">
+        <v>30</v>
+      </c>
+      <c r="H140">
+        <v>975</v>
+      </c>
+      <c r="I140">
+        <v>1.741538</v>
+      </c>
+      <c r="J140">
+        <v>61.326530609999999</v>
+      </c>
+      <c r="K140" t="s">
+        <v>42</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>3005</v>
+      </c>
+      <c r="N140" t="s">
+        <v>170</v>
+      </c>
+      <c r="O140">
+        <v>1698</v>
+      </c>
+      <c r="P140">
+        <v>1769.7290929999999</v>
+      </c>
+      <c r="Q140">
+        <v>49</v>
+      </c>
+      <c r="S140">
+        <v>61.326531000000003</v>
+      </c>
+      <c r="T140">
+        <v>2.885748</v>
+      </c>
+      <c r="U140">
+        <v>51</v>
+      </c>
+      <c r="V140">
+        <v>3.0035340000000001</v>
+      </c>
+      <c r="W140">
+        <v>58.921568999999998</v>
+      </c>
+      <c r="X140">
+        <v>12</v>
+      </c>
+      <c r="Y140">
+        <v>250.41666699999999</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="B141" t="s">
+        <v>26</v>
+      </c>
+      <c r="C141" t="s">
+        <v>206</v>
+      </c>
+      <c r="D141" t="s">
+        <v>194</v>
+      </c>
+      <c r="E141" t="s">
+        <v>29</v>
+      </c>
+      <c r="F141">
+        <v>52</v>
+      </c>
+      <c r="G141" t="s">
+        <v>30</v>
+      </c>
+      <c r="H141">
+        <v>2187</v>
+      </c>
+      <c r="I141">
+        <v>1.1751259999999999</v>
+      </c>
+      <c r="J141">
+        <v>52.61538462</v>
+      </c>
+      <c r="K141" t="s">
+        <v>42</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>2736</v>
+      </c>
+      <c r="N141" t="s">
+        <v>205</v>
+      </c>
+      <c r="O141">
+        <v>2570</v>
+      </c>
+      <c r="P141">
+        <v>1064.5914399999999</v>
+      </c>
+      <c r="Q141">
+        <v>52</v>
+      </c>
+      <c r="S141">
+        <v>52.615385000000003</v>
+      </c>
+      <c r="T141">
+        <v>2.0233460000000001</v>
+      </c>
+      <c r="U141">
+        <v>66</v>
+      </c>
+      <c r="V141">
+        <v>2.5680930000000002</v>
+      </c>
+      <c r="W141">
+        <v>41.454545000000003</v>
+      </c>
+      <c r="X141">
+        <v>43</v>
+      </c>
+      <c r="Y141">
+        <v>63.627907</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>25</v>
+      </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" t="s">
+        <v>204</v>
+      </c>
+      <c r="D142" t="s">
+        <v>28</v>
+      </c>
+      <c r="E142" t="s">
+        <v>29</v>
+      </c>
+      <c r="F142">
+        <v>76</v>
+      </c>
+      <c r="G142" t="s">
+        <v>30</v>
+      </c>
+      <c r="H142">
+        <v>1472</v>
+      </c>
+      <c r="I142">
+        <v>1.1379079999999999</v>
+      </c>
+      <c r="J142">
+        <v>43.736842109999998</v>
+      </c>
+      <c r="K142" t="s">
+        <v>42</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>3324</v>
+      </c>
+      <c r="N142" t="s">
+        <v>203</v>
+      </c>
+      <c r="O142">
+        <v>1675</v>
+      </c>
+      <c r="P142">
+        <v>1984.4776119999999</v>
+      </c>
+      <c r="Q142">
+        <v>76</v>
+      </c>
+      <c r="S142">
+        <v>43.736842000000003</v>
+      </c>
+      <c r="T142">
+        <v>4.5373130000000002</v>
+      </c>
+      <c r="U142">
+        <v>80</v>
+      </c>
+      <c r="V142">
+        <v>4.7761189999999996</v>
+      </c>
+      <c r="W142">
+        <v>41.55</v>
+      </c>
+      <c r="X142">
+        <v>2</v>
+      </c>
+      <c r="Y142">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>25</v>
+      </c>
+      <c r="B143" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" t="s">
+        <v>202</v>
+      </c>
+      <c r="D143" t="s">
+        <v>194</v>
+      </c>
+      <c r="E143" t="s">
+        <v>29</v>
+      </c>
+      <c r="F143">
+        <v>63</v>
+      </c>
+      <c r="G143" t="s">
+        <v>30</v>
+      </c>
+      <c r="H143">
+        <v>2559</v>
+      </c>
+      <c r="I143">
+        <v>1.144979</v>
+      </c>
+      <c r="J143">
+        <v>49.301587300000001</v>
+      </c>
+      <c r="K143" t="s">
+        <v>42</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>3106</v>
+      </c>
+      <c r="N143" t="s">
+        <v>201</v>
+      </c>
+      <c r="O143">
+        <v>2930</v>
+      </c>
+      <c r="P143">
+        <v>1060.0682589999999</v>
+      </c>
+      <c r="Q143">
+        <v>63</v>
+      </c>
+      <c r="S143">
+        <v>49.301586999999998</v>
+      </c>
+      <c r="T143">
+        <v>2.1501709999999998</v>
+      </c>
+      <c r="U143">
+        <v>66</v>
+      </c>
+      <c r="V143">
+        <v>2.2525599999999999</v>
+      </c>
+      <c r="W143">
+        <v>47.060606</v>
+      </c>
+      <c r="X143">
+        <v>42</v>
+      </c>
+      <c r="Y143">
+        <v>73.952381000000003</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>25</v>
+      </c>
+      <c r="B144" t="s">
+        <v>26</v>
+      </c>
+      <c r="C144" t="s">
+        <v>200</v>
+      </c>
+      <c r="D144" t="s">
+        <v>28</v>
+      </c>
+      <c r="E144" t="s">
+        <v>29</v>
+      </c>
+      <c r="F144">
+        <v>78</v>
+      </c>
+      <c r="G144" t="s">
+        <v>41</v>
+      </c>
+      <c r="H144">
+        <v>3466</v>
+      </c>
+      <c r="I144">
+        <v>1.257069</v>
+      </c>
+      <c r="J144">
+        <v>61.358974359999998</v>
+      </c>
+      <c r="K144" t="s">
+        <v>42</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>4786</v>
+      </c>
+      <c r="N144" t="s">
+        <v>199</v>
+      </c>
+      <c r="O144">
+        <v>4357</v>
+      </c>
+      <c r="P144">
+        <v>1098.4622449999999</v>
+      </c>
+      <c r="Q144">
+        <v>91</v>
+      </c>
+      <c r="S144">
+        <v>52.593406999999999</v>
+      </c>
+      <c r="T144">
+        <v>2.0885929999999999</v>
+      </c>
+      <c r="U144">
+        <v>98</v>
+      </c>
+      <c r="V144">
+        <v>2.2492540000000001</v>
+      </c>
+      <c r="W144">
+        <v>48.836734999999997</v>
+      </c>
+      <c r="X144">
+        <v>78</v>
+      </c>
+      <c r="Y144">
+        <v>61.358974000000003</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>25</v>
+      </c>
+      <c r="B145" t="s">
+        <v>26</v>
+      </c>
+      <c r="C145" t="s">
+        <v>169</v>
+      </c>
+      <c r="D145" t="s">
+        <v>194</v>
+      </c>
+      <c r="E145" t="s">
+        <v>29</v>
+      </c>
+      <c r="F145">
+        <v>22</v>
+      </c>
+      <c r="G145" t="s">
+        <v>30</v>
+      </c>
+      <c r="H145">
+        <v>1428</v>
+      </c>
+      <c r="I145">
+        <v>1.0546219999999999</v>
+      </c>
+      <c r="J145">
+        <v>93.454545449999998</v>
+      </c>
+      <c r="K145" t="s">
+        <v>42</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>2056</v>
+      </c>
+      <c r="N145" t="s">
+        <v>198</v>
+      </c>
+      <c r="O145">
+        <v>1506</v>
+      </c>
+      <c r="P145">
+        <v>1365.205843</v>
+      </c>
+      <c r="Q145">
+        <v>22</v>
+      </c>
+      <c r="S145">
+        <v>93.454544999999996</v>
+      </c>
+      <c r="T145">
+        <v>1.460823</v>
+      </c>
+      <c r="U145">
+        <v>26</v>
+      </c>
+      <c r="V145">
+        <v>1.7264280000000001</v>
+      </c>
+      <c r="W145">
+        <v>79.076922999999994</v>
+      </c>
+      <c r="X145">
+        <v>19</v>
+      </c>
+      <c r="Y145">
+        <v>108.210526</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146" t="s">
+        <v>26</v>
+      </c>
+      <c r="C146" t="s">
+        <v>197</v>
+      </c>
+      <c r="D146" t="s">
+        <v>194</v>
+      </c>
+      <c r="E146" t="s">
+        <v>29</v>
+      </c>
+      <c r="F146">
+        <v>22</v>
+      </c>
+      <c r="G146" t="s">
+        <v>30</v>
+      </c>
+      <c r="H146">
+        <v>1376</v>
+      </c>
+      <c r="I146">
+        <v>1.079215</v>
+      </c>
+      <c r="J146">
+        <v>98.227272729999996</v>
+      </c>
+      <c r="K146" t="s">
+        <v>42</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>2161</v>
+      </c>
+      <c r="N146" t="s">
+        <v>196</v>
+      </c>
+      <c r="O146">
+        <v>1485</v>
+      </c>
+      <c r="P146">
+        <v>1455.2188550000001</v>
+      </c>
+      <c r="Q146">
+        <v>22</v>
+      </c>
+      <c r="S146">
+        <v>98.227272999999997</v>
+      </c>
+      <c r="T146">
+        <v>1.481481</v>
+      </c>
+      <c r="U146">
+        <v>23</v>
+      </c>
+      <c r="V146">
+        <v>1.5488219999999999</v>
+      </c>
+      <c r="W146">
+        <v>93.956522000000007</v>
+      </c>
+      <c r="X146">
+        <v>16</v>
+      </c>
+      <c r="Y146">
+        <v>135.0625</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>25</v>
+      </c>
+      <c r="B147" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" t="s">
+        <v>195</v>
+      </c>
+      <c r="D147" t="s">
+        <v>194</v>
+      </c>
+      <c r="E147" t="s">
+        <v>29</v>
+      </c>
+      <c r="F147">
+        <v>65</v>
+      </c>
+      <c r="G147" t="s">
+        <v>41</v>
+      </c>
+      <c r="H147">
+        <v>1707</v>
+      </c>
+      <c r="I147">
+        <v>1.081429</v>
+      </c>
+      <c r="J147">
+        <v>52.2</v>
+      </c>
+      <c r="K147" t="s">
+        <v>42</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>3393</v>
+      </c>
+      <c r="N147" t="s">
+        <v>192</v>
+      </c>
+      <c r="O147">
+        <v>1846</v>
+      </c>
+      <c r="P147">
+        <v>1838.0281689999999</v>
+      </c>
+      <c r="Q147">
+        <v>72</v>
+      </c>
+      <c r="S147">
+        <v>47.125</v>
+      </c>
+      <c r="T147">
+        <v>3.900325</v>
+      </c>
+      <c r="U147">
+        <v>79</v>
+      </c>
+      <c r="V147">
+        <v>4.2795230000000002</v>
+      </c>
+      <c r="W147">
+        <v>42.949367000000002</v>
+      </c>
+      <c r="X147">
+        <v>65</v>
+      </c>
+      <c r="Y147">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>25</v>
+      </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" t="s">
+        <v>193</v>
+      </c>
+      <c r="D148" t="s">
+        <v>102</v>
+      </c>
+      <c r="E148" t="s">
+        <v>29</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="K148" t="s">
+        <v>42</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148" t="s">
+        <v>192</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="U148">
+        <v>0</v>
+      </c>
+      <c r="V148">
+        <v>0</v>
+      </c>
+      <c r="W148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>25</v>
+      </c>
+      <c r="B149" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" t="s">
+        <v>191</v>
+      </c>
+      <c r="D149" t="s">
+        <v>28</v>
+      </c>
+      <c r="E149" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149">
+        <v>132</v>
+      </c>
+      <c r="G149" t="s">
+        <v>41</v>
+      </c>
+      <c r="H149">
+        <v>3450</v>
+      </c>
+      <c r="I149">
+        <v>1.4350719999999999</v>
+      </c>
+      <c r="J149">
+        <v>38.787878790000001</v>
+      </c>
+      <c r="K149" t="s">
+        <v>42</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>5120</v>
+      </c>
+      <c r="N149" t="s">
+        <v>62</v>
+      </c>
+      <c r="O149">
+        <v>4951</v>
+      </c>
+      <c r="P149">
+        <v>1034.1345180000001</v>
+      </c>
+      <c r="Q149">
+        <v>145</v>
+      </c>
+      <c r="S149">
+        <v>35.310344999999998</v>
+      </c>
+      <c r="T149">
+        <v>2.9287010000000002</v>
+      </c>
+      <c r="U149">
+        <v>166</v>
+      </c>
+      <c r="V149">
+        <v>3.3528579999999999</v>
+      </c>
+      <c r="W149">
+        <v>30.843373</v>
+      </c>
+      <c r="X149">
+        <v>132</v>
+      </c>
+      <c r="Y149">
+        <v>38.787878999999997</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>25</v>
+      </c>
+      <c r="B150" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150" t="s">
+        <v>190</v>
+      </c>
+      <c r="D150" t="s">
+        <v>28</v>
+      </c>
+      <c r="E150" t="s">
+        <v>29</v>
+      </c>
+      <c r="F150">
+        <v>28</v>
+      </c>
+      <c r="G150" t="s">
+        <v>41</v>
+      </c>
+      <c r="H150">
+        <v>4340</v>
+      </c>
+      <c r="I150">
+        <v>1.3988480000000001</v>
+      </c>
+      <c r="J150">
+        <v>186.82142856999999</v>
+      </c>
+      <c r="K150" t="s">
+        <v>42</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>5231</v>
+      </c>
+      <c r="N150" t="s">
+        <v>70</v>
+      </c>
+      <c r="O150">
+        <v>6071</v>
+      </c>
+      <c r="P150">
+        <v>861.637292</v>
+      </c>
+      <c r="Q150">
+        <v>66</v>
+      </c>
+      <c r="S150">
+        <v>79.257576</v>
+      </c>
+      <c r="T150">
+        <v>1.0871360000000001</v>
+      </c>
+      <c r="U150">
+        <v>83</v>
+      </c>
+      <c r="V150">
+        <v>1.3671549999999999</v>
+      </c>
+      <c r="W150">
+        <v>63.024096</v>
+      </c>
+      <c r="X150">
+        <v>28</v>
+      </c>
+      <c r="Y150">
+        <v>186.82142899999999</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>